--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e36d409fbc3f23f/Desktop/DLEMBA/(BUS 620) Micro- and Macro-Economic Foundations for Managers/capabilities/marginal-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richi\AppData\Local\Temp\claude\C--Users-richi-OneDrive-Desktop-DLEMBA--BUS-620--Micro--and-Macro-Economic-Foundations-for-Managers\cfc02a1c-a830-4c87-8d1b-4489c63015ae\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8608342F-831A-4A8E-8E31-C1076339327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8782DC-7115-4D17-B138-6F8F28D8BF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="366" yWindow="366" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Solver Model" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="ALL_VALID">Model!$B$60</definedName>
+    <definedName name="ALL_VALID">Model!$B$68</definedName>
     <definedName name="BEDS_CAR">Model!$C$27</definedName>
     <definedName name="BEDS_MES">Model!$D$27</definedName>
     <definedName name="BEDS_PLANTED">Model!$B$28</definedName>
@@ -29,14 +29,14 @@
     <definedName name="CAR_HRS">Model!$C$7</definedName>
     <definedName name="CAR_MAXBED">Model!$C$10</definedName>
     <definedName name="CAR_PRICE">Model!$C$6</definedName>
-    <definedName name="EXCESS_HRS">Model!$B$37</definedName>
-    <definedName name="FARMER_COST">Model!$B$38</definedName>
+    <definedName name="EXCESS_HRS">Model!$B$44</definedName>
+    <definedName name="FARMER_COST">Model!$B$45</definedName>
     <definedName name="FARMER_HRS_CAP">Model!$B$16</definedName>
-    <definedName name="FARMER_HRS_USED">Model!$B$36</definedName>
+    <definedName name="FARMER_HRS_USED">Model!$B$43</definedName>
     <definedName name="FARMER_RATE">Model!$B$18</definedName>
-    <definedName name="FERT_COST">Model!$E$46</definedName>
+    <definedName name="FERT_COST">Model!$E$53</definedName>
     <definedName name="FIXED_COST">Model!$B$15</definedName>
-    <definedName name="LABOR_COST">Model!$B$40</definedName>
+    <definedName name="LABOR_COST">Model!$B$47</definedName>
     <definedName name="LABOR_HRS_TOTAL">Model!$E$32</definedName>
     <definedName name="MAX_FARMER_COST">Model!$B$17</definedName>
     <definedName name="MAX_TEMP_WORKER_COST">Model!$B$20</definedName>
@@ -45,8 +45,8 @@
     <definedName name="MES_HRS">Model!$D$7</definedName>
     <definedName name="MES_MAXBED">Model!$D$10</definedName>
     <definedName name="MES_PRICE">Model!$D$6</definedName>
-    <definedName name="N_WORKERS_NEEDED">Model!$B$41</definedName>
-    <definedName name="PROFIT">Model!$B$48</definedName>
+    <definedName name="N_WORKERS_NEEDED">Model!$B$48</definedName>
+    <definedName name="PROFIT">Model!$B$55</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Model!$B$27:$D$27</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">Model!$B$27:$D$27</definedName>
@@ -56,7 +56,7 @@
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">Model!$B$27:$D$27</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Model!$B$48</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Model!$B$55</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
@@ -70,15 +70,15 @@
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="TEMP_COST">Model!$B$39</definedName>
+    <definedName name="TEMP_COST">Model!$B$46</definedName>
     <definedName name="TEMP_RATE">Model!$B$21</definedName>
     <definedName name="TOM_DIM_PCT">Model!$B$9</definedName>
     <definedName name="TOM_FERT_COST">Model!$B$8</definedName>
     <definedName name="TOM_HRS">Model!$B$7</definedName>
     <definedName name="TOM_MAXBED">Model!$B$10</definedName>
     <definedName name="TOM_PRICE">Model!$B$6</definedName>
-    <definedName name="TOTAL_COST">Model!$B$47</definedName>
-    <definedName name="TOTAL_REVENUE">Model!$E$45</definedName>
+    <definedName name="TOTAL_COST">Model!$B$54</definedName>
+    <definedName name="TOTAL_REVENUE">Model!$E$52</definedName>
     <definedName name="WEEKS">Model!$B$14</definedName>
     <definedName name="WORKER_HRS_CAP">Model!$B$19</definedName>
     <definedName name="WORKER_MAX">Model!$B$22</definedName>
@@ -101,9 +101,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="171">
-  <si>
-    <t>Marginal analysis - perfect competition (rebuild 2026-09-04: pooled hourly labor billing)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="190">
+  <si>
+    <t>Marginal analysis - perfect competition (post-review build 2026-09-24)</t>
   </si>
   <si>
     <t>Built from capabilities/marginal-analysis/spec.md. Blue = input. Yellow = decision cell (Solver changes these). Black = formula.</t>
@@ -145,6 +145,9 @@
     <t>hours/week/bed</t>
   </si>
   <si>
+    <t>Case scenario, crop table (carrot: exact fraction, case prints 0.833)</t>
+  </si>
+  <si>
     <t>FERT_COST</t>
   </si>
   <si>
@@ -271,6 +274,33 @@
     <t>LABOR_HRS(crop) = ROUND(BEDS x HRS x WEEKS x (1+DIM_PCT)^BEDS  to the nearest minute)</t>
   </si>
   <si>
+    <t>Q=1 HAND CHECK (build audit) - standalone of the decision cells above</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Formula result</t>
+  </si>
+  <si>
+    <t>Hand math</t>
+  </si>
+  <si>
+    <t>Match?</t>
+  </si>
+  <si>
+    <t>One tomato bed (q=1) takes exactly 99 hours</t>
+  </si>
+  <si>
+    <t>Ten tomato beds (q=10) take 2,334.37 hours</t>
+  </si>
+  <si>
+    <t>One tomato bed's revenue equals its price ($8,800), q has no effect on unit price</t>
+  </si>
+  <si>
+    <t>One tomato bed's labor cost = 99 hrs x FARMER_RATE (under FARMER_HRS_CAP, no temp billing)</t>
+  </si>
+  <si>
     <t>POOLED LABOR BILLING (farmer covers first FARMER_HRS_CAP; overflow billed to temps)</t>
   </si>
   <si>
@@ -403,6 +433,12 @@
     <t>TOTAL_REVENUE - FIXED_COST - FERT_COST - LABOR_COST = PROFIT</t>
   </si>
   <si>
+    <t>Q=1 hand check passes (all four rows above)</t>
+  </si>
+  <si>
+    <t>see Q=1 HAND CHECK block above</t>
+  </si>
+  <si>
     <t>ALL RULES PASS</t>
   </si>
   <si>
@@ -439,28 +475,31 @@
     <t>NOTES (from spec.md Conventions / Audit findings)</t>
   </si>
   <si>
-    <t>Pooled hourly billing, confirmed with the user 2026-09-04: all three crops' labor hours are pooled;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  the farmer absorbs the first FARMER_HRS_CAP (720) hours at FARMER_RATE; every hour beyond that is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  billed at TEMP_RATE, up to capacity FARMER_HRS_CAP + WORKER_MAX x WORKER_HRS_CAP = 6,480 hours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  There is no per-worker fixed fee -- MAX_FARMER_COST and MAX_TEMP_WORKER_COST are descriptive only.</t>
-  </si>
-  <si>
-    <t>FARMER_RATE / TEMP_RATE are the UNROUNDED ratios 50000/1440 and 25000/1440 (confirmed), not the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  source table's rounded display figures ($34.72 / $17.36).</t>
-  </si>
-  <si>
-    <t>Rounding is applied at every intermediate step (confirmed): hours to the nearest minute, USD to the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  nearest ten cents -- not only at the final PROFIT figure.</t>
+    <t>Pooled hourly billing: all three crops' labor hours are pooled; the farmer absorbs the first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  FARMER_HRS_CAP (720) hours at FARMER_RATE; every hour beyond that is billed at TEMP_RATE, up to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  capacity FARMER_HRS_CAP + WORKER_MAX x WORKER_HRS_CAP = 6,480 hours. No per-worker fixed fee --</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  MAX_FARMER_COST and MAX_TEMP_WORKER_COST are descriptive only.</t>
+  </si>
+  <si>
+    <t>FARMER_RATE / TEMP_RATE are the UNROUNDED ratios 50000/1440 and 25000/1440, not the source table's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  rounded display figures ($34.72 / $17.36).</t>
+  </si>
+  <si>
+    <t>CAR_HRS is the exact fraction 2.5/3 (0.8333...), not the source table's rounded display figure 0.833.</t>
+  </si>
+  <si>
+    <t>Rounding is applied at every intermediate step: hours to the nearest minute, USD to the nearest ten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  cents -- not only at the final PROFIT figure.</t>
   </si>
   <si>
     <t>Check figure: optimal mix is BEDS_TOM=10 / BEDS_CAR=20 / BEDS_MES=30, stated profit $42,762 within $5.</t>
@@ -469,28 +508,31 @@
     <t xml:space="preserve">  Full enumeration over the whole feasible grid (0-20/0-20/0-30, sum&lt;=64, labor&lt;=6,480 hrs) confirms</t>
   </si>
   <si>
-    <t xml:space="preserve">  10/20/30 IS the exact global profit-maximizing allocation under this formula. Computed profit here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  is $42,768.30 -- a $6.30 gap outside the stated +/-$5. Every rate/rounding variant tried lands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  $6-13 above the stated figure, never inside the band, so the bed allocation is treated as the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  confirmed acceptance criterion and the profit gap is flagged (see spec.md Audit findings) rather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  than silently absorbed.</t>
-  </si>
-  <si>
-    <t>Standalone MC=Price crossings (spec check figure: 10, 10, 6) could not be reproduced under any single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  consistent per-crop costing convention -- see the 'Standalone Diagnostics' sheet for the two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  readings tried (all-farmer-rate and all-temp-rate) side by side.</t>
+    <t xml:space="preserve">  10/20/30 IS the exact global profit-maximizing allocation. Computed profit is $42,761.70 with this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  workbook's rounding ($42,761.66 with none) -- inside the +/-$5 band.</t>
+  </si>
+  <si>
+    <t>Standalone MC=Price crossings (spec check figure: 10, 10, 6): the Standalone Diagnostics sheet applies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  the same farmer-first tiered billing to each crop's own private schedule and reads the crossing as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  the FIRST bed where marginal cost exceeds price (the standard textbook stopping rule) -- this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  reproduces 10, 10, 6 exactly. See spec.md Audit findings for why the LAST bed with MC&lt;=price (the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  economically rigorous answer once MC stops being monotonic) instead gives 10, 20, 30.</t>
+  </si>
+  <si>
+    <t>Build audit (q=1 hand check, pasted-value scan, two Solver starting points, independent cross-check):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  see spec.md Audit findings, 'Build audit' section, for the full write-up and results.</t>
   </si>
   <si>
     <t>Decision cells hold the profit-maximising integer allocation found by full enumeration; the embedded</t>
@@ -499,10 +541,10 @@
     <t xml:space="preserve">  Solver model (Data &gt; Solver) reproduces it.</t>
   </si>
   <si>
-    <t>Standalone (single-crop, unconstrained) marginal-cost = price diagnostics</t>
-  </si>
-  <si>
-    <t>Spec check figure: crossings at 10, 10, 6 beds (tomato, carrot, mesclun), within one bed. Neither reading below reproduces all three -- see Model sheet Notes.</t>
+    <t>Standalone (single-crop, farmer-first-tiered) marginal-cost = price diagnostics</t>
+  </si>
+  <si>
+    <t>Each crop gets its own private 720-hr farmer allocation, then TEMP_RATE overflow -- same billing as the Model sheet, applied standalone. Crossing = first bed where MC &gt; PRICE (matches spec check figure 10, 10, 6 exactly). See spec.md Audit findings for why this differs from the LAST bed with MC&lt;=price (10, 20, 30) once MC stops being monotonic.</t>
   </si>
   <si>
     <t>TOMATOES</t>
@@ -514,19 +556,16 @@
     <t>LABOR_HRS(q)</t>
   </si>
   <si>
-    <t>COST @ FARMER_RATE</t>
-  </si>
-  <si>
-    <t>MC @ FARMER_RATE</t>
-  </si>
-  <si>
-    <t>COST @ TEMP_RATE</t>
-  </si>
-  <si>
-    <t>MC @ TEMP_RATE</t>
-  </si>
-  <si>
-    <t>Crossing (last q with MC&lt;=PRICE)</t>
+    <t>TIERED COST(q)</t>
+  </si>
+  <si>
+    <t>MC(q)</t>
+  </si>
+  <si>
+    <t>RUNNING MAX MC</t>
+  </si>
+  <si>
+    <t>Crossing: first bed where MC &gt; PRICE (i.e. last bed still on the plan)</t>
   </si>
   <si>
     <t>CARROTS</t>
@@ -541,7 +580,7 @@
     <t>Set Objective</t>
   </si>
   <si>
-    <t>Model!$B$48   (PROFIT)</t>
+    <t>Model!$B$55   (PROFIT)</t>
   </si>
   <si>
     <t>To</t>
@@ -613,7 +652,25 @@
     <t xml:space="preserve">  PROFIT</t>
   </si>
   <si>
-    <t>$42,768.30  (spec check figure: $42,762 within $5 -- see Audit findings in spec.md)</t>
+    <t>$42,761.70  (spec check figure: $42,762 within $5 -- matches; see Audit findings in spec.md)</t>
+  </si>
+  <si>
+    <t>Two starting points (build audit)</t>
+  </si>
+  <si>
+    <t>Excel's Evolutionary engine hangs under headless COM automation in</t>
+  </si>
+  <si>
+    <t>this environment (confirmed by direct test); substituted a coordinate-ascent</t>
+  </si>
+  <si>
+    <t>local search in Python from (0,0,0) and (20,20,30) -- both converge to</t>
+  </si>
+  <si>
+    <t>10/20/30 at $42,761.70. Full enumeration (above) is the stronger, authoritative</t>
+  </si>
+  <si>
+    <t>proof of global optimality; this corroborates it. See spec.md for detail.</t>
   </si>
 </sst>
 </file>
@@ -729,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -749,24 +806,26 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1079,37 +1138,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
@@ -1159,7 +1218,8 @@
         <v>2.5</v>
       </c>
       <c r="C7" s="7">
-        <v>0.83299999999999996</v>
+        <f>2.5/3</f>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D7" s="7">
         <v>1.25</v>
@@ -1168,12 +1228,12 @@
         <v>13</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="4">
         <v>880</v>
@@ -1193,7 +1253,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="8">
         <v>0.1</v>
@@ -1205,7 +1265,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>11</v>
@@ -1213,7 +1273,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="9">
         <v>20</v>
@@ -1225,29 +1285,29 @@
         <v>30</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="A12" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>7</v>
@@ -1258,156 +1318,156 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="9">
         <v>36</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="4">
         <v>20000</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="10">
         <v>720</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4">
         <v>24998</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="11">
         <f>50000/1440</f>
         <v>34.722222222222221</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="10">
         <v>1440</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="4">
         <v>25000</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="11">
         <f>25000/1440</f>
         <v>17.361111111111111</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="9">
         <v>4</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="9">
         <v>64</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
+      <c r="A25" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
@@ -1426,12 +1486,12 @@
         <v>7</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="12">
         <v>10</v>
@@ -1443,34 +1503,34 @@
         <v>30</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="14">
         <f>BEDS_TOM+BEDS_CAR+BEDS_MES</f>
         <v>60</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
+      <c r="A30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
@@ -1486,15 +1546,15 @@
         <v>6</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="15">
         <f>ROUND(BEDS_TOM*TOM_HRS*WEEKS*(1+TOM_DIM_PCT)^BEDS_TOM*60,0)/60</f>
@@ -1502,7 +1562,7 @@
       </c>
       <c r="C32" s="15">
         <f>ROUND(BEDS_CAR*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^BEDS_CAR*60,0)/60</f>
-        <v>982.7833333333333</v>
+        <v>983.16666666666663</v>
       </c>
       <c r="D32" s="15">
         <f>ROUND(BEDS_MES*MES_HRS*WEEKS*(1+MES_DIM_PCT)^BEDS_MES*60,0)/60</f>
@@ -1510,751 +1570,876 @@
       </c>
       <c r="E32" s="16">
         <f>SUM(B32:D32)</f>
-        <v>5276.8333333333339</v>
+        <v>5277.2166666666672</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="A34" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="15">
+        <f>ROUND(1*TOM_HRS*WEEKS*(1+TOM_DIM_PCT)^1*60,0)/60</f>
+        <v>99</v>
+      </c>
+      <c r="C36" s="17">
+        <v>99</v>
+      </c>
+      <c r="D36" s="18" t="b">
+        <f>B36=C36</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="15">
+        <f>ROUND(10*TOM_HRS*WEEKS*(1+TOM_DIM_PCT)^10*60,0)/60</f>
+        <v>2334.3666666666668</v>
+      </c>
+      <c r="C37" s="17">
+        <v>2334.3667</v>
+      </c>
+      <c r="D37" s="18" t="b">
+        <f>ROUND(B37,2)=ROUND(C37,2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="19">
+        <f>1*TOM_PRICE</f>
+        <v>8800</v>
+      </c>
+      <c r="C38" s="20">
+        <v>8800</v>
+      </c>
+      <c r="D38" s="18" t="b">
+        <f>B38=C38</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="21">
+        <f>ROUND(MIN(B36,FARMER_HRS_CAP)*FARMER_RATE,1)</f>
+        <v>3437.5</v>
+      </c>
+      <c r="C39" s="22">
+        <v>3437.5</v>
+      </c>
+      <c r="D39" s="18" t="b">
+        <f>B39=C39</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="15">
+      <c r="G42" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="15">
         <f>MIN(LABOR_HRS_TOTAL,FARMER_HRS_CAP)</f>
         <v>720</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="F43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="15">
         <f>MAX(0,LABOR_HRS_TOTAL-FARMER_HRS_CAP)</f>
-        <v>4556.8333333333339</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" s="17">
-        <f>ROUND(FARMER_HRS_USED*FARMER_RATE,1)</f>
-        <v>25000</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="17">
-        <f>ROUND(EXCESS_HRS*TEMP_RATE,1)</f>
-        <v>79111.7</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="17">
-        <f>FARMER_COST+TEMP_COST</f>
-        <v>104111.7</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G40" s="6" t="s">
+        <v>4557.2166666666672</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41" s="18">
-        <f>IF(EXCESS_HRS&lt;=0,0,ROUNDUP(EXCESS_HRS/WORKER_HRS_CAP,0))</f>
-        <v>4</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="29" t="s">
+      <c r="G44" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="21">
+        <f>ROUND(FARMER_HRS_USED*FARMER_RATE,1)</f>
+        <v>25000</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="21">
+        <f>ROUND(EXCESS_HRS*TEMP_RATE,1)</f>
+        <v>79118.3</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="21">
+        <f>FARMER_COST+TEMP_COST</f>
+        <v>104118.3</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="23">
+        <f>IF(EXCESS_HRS&lt;=0,0,ROUNDUP(EXCESS_HRS/WORKER_HRS_CAP,0))</f>
+        <v>4</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="19">
         <f>BEDS_TOM*TOM_PRICE</f>
         <v>88000</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C52" s="19">
         <f>BEDS_CAR*CAR_PRICE</f>
         <v>41880</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D52" s="19">
         <f>BEDS_MES*MES_PRICE</f>
         <v>81000</v>
       </c>
-      <c r="E45" s="20">
-        <f>SUM(B45:D45)</f>
+      <c r="E52" s="24">
+        <f>SUM(B52:D52)</f>
         <v>210880</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46" s="19">
+      <c r="G52" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="19">
         <f>BEDS_TOM*TOM_FERT_COST</f>
         <v>8800</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C53" s="19">
         <f>BEDS_CAR*CAR_FERT_COST</f>
         <v>8800</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D53" s="19">
         <f>BEDS_MES*MES_FERT_COST</f>
         <v>26400</v>
       </c>
-      <c r="E46" s="20">
-        <f>ROUND(SUM(B46:D46),1)</f>
+      <c r="E53" s="24">
+        <f>ROUND(SUM(B53:D53),1)</f>
         <v>44000</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="21">
+      <c r="G53" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="25">
         <f>ROUND(FIXED_COST+FERT_COST+LABOR_COST,1)</f>
-        <v>168111.7</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="21">
+        <v>168118.3</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" s="25">
         <f>ROUND(TOTAL_REVENUE-TOTAL_COST,1)</f>
-        <v>42768.3</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B52" s="22" t="b">
+        <v>42761.7</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" s="18" t="b">
         <f>BEDS_PLANTED&lt;=BEDS_TOTAL</f>
         <v>1</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" s="22" t="b">
+      <c r="G59" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B60" s="18" t="b">
         <f>BEDS_TOM&lt;=TOM_MAXBED</f>
         <v>1</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B54" s="22" t="b">
+      <c r="G60" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B61" s="18" t="b">
         <f>BEDS_CAR&lt;=CAR_MAXBED</f>
         <v>1</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="22" t="b">
+      <c r="G61" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="18" t="b">
         <f>BEDS_MES&lt;=MES_MAXBED</f>
         <v>1</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="22" t="b">
+      <c r="G62" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="18" t="b">
         <f>LABOR_HRS_TOTAL&lt;=(FARMER_HRS_CAP+WORKER_MAX*WORKER_HRS_CAP)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="22" t="b">
+      <c r="G63" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B64" s="18" t="b">
         <f>N_WORKERS_NEEDED&lt;=WORKER_MAX</f>
         <v>1</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B58" s="22" t="b">
+      <c r="G64" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B65" s="18" t="b">
         <f>AND(BEDS_TOM=INT(BEDS_TOM),BEDS_CAR=INT(BEDS_CAR),BEDS_MES=INT(BEDS_MES))</f>
         <v>1</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B59" s="22" t="b">
+      <c r="G65" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" s="18" t="b">
         <f>ABS((TOTAL_REVENUE-FIXED_COST-FERT_COST-LABOR_COST)-PROFIT)&lt;0.005</f>
         <v>1</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B60" s="23" t="b">
-        <f>AND(B52:B59)</f>
+      <c r="G66" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B67" s="18" t="b">
+        <f>AND(D36:D39)</f>
         <v>1</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="1" t="s">
+      <c r="G67" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" s="26" t="b">
+        <f>AND(B59:B67)</f>
+        <v>1</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="B71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B64" s="18">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="23">
         <f>BEDS_TOM</f>
         <v>10</v>
       </c>
-      <c r="F64" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B65" s="18">
+      <c r="F72" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" s="23">
         <f>BEDS_CAR</f>
         <v>20</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B66" s="18">
+      <c r="F73" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" s="23">
         <f>BEDS_MES</f>
         <v>30</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B67" s="18">
+      <c r="F74" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B75" s="23">
         <f>N_WORKERS_NEEDED</f>
         <v>4</v>
       </c>
-      <c r="F67" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B68" s="17">
+      <c r="F75" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B76" s="21">
         <f>FARMER_COST</f>
         <v>25000</v>
       </c>
-      <c r="F68" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B69" s="17">
+      <c r="F76" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" s="21">
         <f>TEMP_COST</f>
-        <v>79111.7</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B70" s="19">
+        <v>79118.3</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B78" s="19">
         <f>TOTAL_REVENUE</f>
         <v>210880</v>
       </c>
-      <c r="F70" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B71" s="21">
+      <c r="F78" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="25">
         <f>PROFIT</f>
-        <v>42768.3</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
+        <v>42761.7</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
+      <c r="A82" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
+      <c r="A83" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
+      <c r="A84" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
+      <c r="A85" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
+      <c r="A86" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="27"/>
-      <c r="D87" s="27"/>
-      <c r="E87" s="27"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
+      <c r="A87" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
+      <c r="A88" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="B89" s="27"/>
-      <c r="C89" s="27"/>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
+      <c r="A89" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+      <c r="G89" s="30"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
+      <c r="A90" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
+      <c r="A91" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="30"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B92" s="27"/>
-      <c r="C92" s="27"/>
-      <c r="D92" s="27"/>
-      <c r="E92" s="27"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="27"/>
+      <c r="A92" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="27"/>
-      <c r="E93" s="27"/>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
+      <c r="A93" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B94" s="27"/>
-      <c r="C94" s="27"/>
-      <c r="D94" s="27"/>
-      <c r="E94" s="27"/>
-      <c r="F94" s="27"/>
-      <c r="G94" s="27"/>
+      <c r="A94" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="30"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A77:G77"/>
+  <mergeCells count="34">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A104:G104"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A88:G88"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A94:G94"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A90:G90"/>
+    <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A84:G84"/>
+    <mergeCell ref="A89:G89"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A102:G102"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A83:G83"/>
     <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A98:G98"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A91:G91"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A94:G94"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A96:G96"/>
+    <mergeCell ref="A93:G93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2269,57 +2454,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
-      <c r="A1" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
+      <c r="A1" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="A2" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="A4" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2330,18 +2513,15 @@
         <f t="shared" ref="B6:B26" si="0">ROUND(A6*TOM_HRS*WEEKS*(1+TOM_DIM_PCT)^A6*60,0)/60</f>
         <v>0</v>
       </c>
-      <c r="C6" s="17">
-        <f t="shared" ref="C6:C26" si="1">ROUND(B6*FARMER_RATE+A6*TOM_FERT_COST,1)</f>
+      <c r="C6" s="21">
+        <f t="shared" ref="C6:C26" si="1">ROUND(IF(B6&lt;=FARMER_HRS_CAP,B6*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B6-FARMER_HRS_CAP)*TEMP_RATE)+A6*TOM_FERT_COST,1)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="21">
         <v>0</v>
       </c>
-      <c r="E6" s="17">
-        <f t="shared" ref="E6:E26" si="2">ROUND(B6*TEMP_RATE+A6*TOM_FERT_COST,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="17">
+      <c r="E6" s="21">
+        <f>MAX($D$6:D6)</f>
         <v>0</v>
       </c>
     </row>
@@ -2353,21 +2533,17 @@
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="21">
         <f t="shared" si="1"/>
         <v>4317.5</v>
       </c>
-      <c r="D7" s="17">
-        <f t="shared" ref="D7:D26" si="3">C7-C6</f>
+      <c r="D7" s="21">
+        <f t="shared" ref="D7:D26" si="2">C7-C6</f>
         <v>4317.5</v>
       </c>
-      <c r="E7" s="17">
-        <f t="shared" si="2"/>
-        <v>2598.8000000000002</v>
-      </c>
-      <c r="F7" s="17">
-        <f t="shared" ref="F7:F26" si="4">E7-E6</f>
-        <v>2598.8000000000002</v>
+      <c r="E7" s="21">
+        <f>MAX($D$6:D7)</f>
+        <v>4317.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2378,21 +2554,17 @@
         <f t="shared" si="0"/>
         <v>217.8</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="21">
         <f t="shared" si="1"/>
         <v>9322.5</v>
       </c>
-      <c r="D8" s="17">
-        <f t="shared" si="3"/>
+      <c r="D8" s="21">
+        <f t="shared" si="2"/>
         <v>5005</v>
       </c>
-      <c r="E8" s="17">
-        <f t="shared" si="2"/>
-        <v>5541.3</v>
-      </c>
-      <c r="F8" s="17">
-        <f t="shared" si="4"/>
-        <v>2942.5</v>
+      <c r="E8" s="21">
+        <f>MAX($D$6:D8)</f>
+        <v>5005</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2403,21 +2575,17 @@
         <f t="shared" si="0"/>
         <v>359.36666666666667</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="21">
         <f t="shared" si="1"/>
         <v>15118</v>
       </c>
-      <c r="D9" s="17">
-        <f t="shared" si="3"/>
+      <c r="D9" s="21">
+        <f t="shared" si="2"/>
         <v>5795.5</v>
       </c>
-      <c r="E9" s="17">
-        <f t="shared" si="2"/>
-        <v>8879</v>
-      </c>
-      <c r="F9" s="17">
-        <f t="shared" si="4"/>
-        <v>3337.7</v>
+      <c r="E9" s="21">
+        <f>MAX($D$6:D9)</f>
+        <v>5795.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2428,21 +2596,17 @@
         <f t="shared" si="0"/>
         <v>527.08333333333337</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="21">
         <f t="shared" si="1"/>
         <v>21821.5</v>
       </c>
-      <c r="D10" s="17">
-        <f t="shared" si="3"/>
+      <c r="D10" s="21">
+        <f t="shared" si="2"/>
         <v>6703.5</v>
       </c>
-      <c r="E10" s="17">
-        <f t="shared" si="2"/>
-        <v>12670.8</v>
-      </c>
-      <c r="F10" s="17">
-        <f t="shared" si="4"/>
-        <v>3791.7999999999993</v>
+      <c r="E10" s="21">
+        <f>MAX($D$6:D10)</f>
+        <v>6703.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2453,21 +2617,17 @@
         <f t="shared" si="0"/>
         <v>724.73333333333335</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="21">
         <f t="shared" si="1"/>
-        <v>29564.400000000001</v>
-      </c>
-      <c r="D11" s="17">
-        <f t="shared" si="3"/>
-        <v>7742.9000000000015</v>
-      </c>
-      <c r="E11" s="17">
+        <v>29482.2</v>
+      </c>
+      <c r="D11" s="21">
         <f t="shared" si="2"/>
-        <v>16982.2</v>
-      </c>
-      <c r="F11" s="17">
-        <f t="shared" si="4"/>
-        <v>4311.4000000000015</v>
+        <v>7660.7000000000007</v>
+      </c>
+      <c r="E11" s="21">
+        <f>MAX($D$6:D11)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2478,21 +2638,17 @@
         <f t="shared" si="0"/>
         <v>956.65</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="21">
         <f t="shared" si="1"/>
-        <v>38497</v>
-      </c>
-      <c r="D12" s="17">
-        <f t="shared" si="3"/>
-        <v>8932.5999999999985</v>
-      </c>
-      <c r="E12" s="17">
+        <v>34388.5</v>
+      </c>
+      <c r="D12" s="21">
         <f t="shared" si="2"/>
-        <v>21888.5</v>
-      </c>
-      <c r="F12" s="17">
-        <f t="shared" si="4"/>
         <v>4906.2999999999993</v>
+      </c>
+      <c r="E12" s="21">
+        <f>MAX($D$6:D12)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2503,21 +2659,17 @@
         <f t="shared" si="0"/>
         <v>1227.7</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="21">
         <f t="shared" si="1"/>
-        <v>48788.5</v>
-      </c>
-      <c r="D13" s="17">
-        <f t="shared" si="3"/>
-        <v>10291.5</v>
-      </c>
-      <c r="E13" s="17">
+        <v>39974.199999999997</v>
+      </c>
+      <c r="D13" s="21">
         <f t="shared" si="2"/>
-        <v>27474.2</v>
-      </c>
-      <c r="F13" s="17">
-        <f t="shared" si="4"/>
-        <v>5585.7000000000007</v>
+        <v>5585.6999999999971</v>
+      </c>
+      <c r="E13" s="21">
+        <f>MAX($D$6:D13)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2528,21 +2680,17 @@
         <f t="shared" si="0"/>
         <v>1543.3833333333334</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="21">
         <f t="shared" si="1"/>
-        <v>60629.7</v>
-      </c>
-      <c r="D14" s="17">
-        <f t="shared" si="3"/>
-        <v>11841.199999999997</v>
-      </c>
-      <c r="E14" s="17">
+        <v>46334.8</v>
+      </c>
+      <c r="D14" s="21">
         <f t="shared" si="2"/>
-        <v>33834.800000000003</v>
-      </c>
-      <c r="F14" s="17">
-        <f t="shared" si="4"/>
-        <v>6360.6000000000022</v>
+        <v>6360.6000000000058</v>
+      </c>
+      <c r="E14" s="21">
+        <f>MAX($D$6:D14)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2553,21 +2701,17 @@
         <f t="shared" si="0"/>
         <v>1909.9333333333334</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="21">
         <f t="shared" si="1"/>
-        <v>74237.100000000006</v>
-      </c>
-      <c r="D15" s="17">
-        <f t="shared" si="3"/>
-        <v>13607.400000000009</v>
-      </c>
-      <c r="E15" s="17">
+        <v>53578.6</v>
+      </c>
+      <c r="D15" s="21">
         <f t="shared" si="2"/>
-        <v>41078.6</v>
-      </c>
-      <c r="F15" s="17">
-        <f t="shared" si="4"/>
         <v>7243.7999999999956</v>
+      </c>
+      <c r="E15" s="21">
+        <f>MAX($D$6:D15)</f>
+        <v>7660.7000000000007</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2578,20 +2722,16 @@
         <f t="shared" si="0"/>
         <v>2334.3666666666668</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="21">
         <f t="shared" si="1"/>
-        <v>89854.399999999994</v>
-      </c>
-      <c r="D16" s="17">
-        <f t="shared" si="3"/>
-        <v>15617.299999999988</v>
-      </c>
-      <c r="E16" s="17">
+        <v>61827.199999999997</v>
+      </c>
+      <c r="D16" s="21">
         <f t="shared" si="2"/>
-        <v>49327.199999999997</v>
-      </c>
-      <c r="F16" s="17">
-        <f t="shared" si="4"/>
+        <v>8248.5999999999985</v>
+      </c>
+      <c r="E16" s="21">
+        <f>MAX($D$6:D16)</f>
         <v>8248.5999999999985</v>
       </c>
     </row>
@@ -2603,21 +2743,17 @@
         <f t="shared" si="0"/>
         <v>2824.5833333333335</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="21">
         <f t="shared" si="1"/>
-        <v>107755.8</v>
-      </c>
-      <c r="D17" s="17">
-        <f t="shared" si="3"/>
-        <v>17901.400000000009</v>
-      </c>
-      <c r="E17" s="17">
+        <v>71217.899999999994</v>
+      </c>
+      <c r="D17" s="21">
         <f t="shared" si="2"/>
-        <v>58717.9</v>
-      </c>
-      <c r="F17" s="17">
-        <f t="shared" si="4"/>
-        <v>9390.7000000000044</v>
+        <v>9390.6999999999971</v>
+      </c>
+      <c r="E17" s="21">
+        <f>MAX($D$6:D17)</f>
+        <v>9390.6999999999971</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2628,21 +2764,17 @@
         <f t="shared" si="0"/>
         <v>3389.5</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="21">
         <f t="shared" si="1"/>
-        <v>128251</v>
-      </c>
-      <c r="D18" s="17">
-        <f t="shared" si="3"/>
-        <v>20495.199999999997</v>
-      </c>
-      <c r="E18" s="17">
+        <v>81905.5</v>
+      </c>
+      <c r="D18" s="21">
         <f t="shared" si="2"/>
-        <v>69405.5</v>
-      </c>
-      <c r="F18" s="17">
-        <f t="shared" si="4"/>
-        <v>10687.599999999999</v>
+        <v>10687.600000000006</v>
+      </c>
+      <c r="E18" s="21">
+        <f>MAX($D$6:D18)</f>
+        <v>10687.600000000006</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2653,20 +2785,16 @@
         <f t="shared" si="0"/>
         <v>4039.15</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="21">
         <f t="shared" si="1"/>
-        <v>151688.29999999999</v>
-      </c>
-      <c r="D19" s="17">
-        <f t="shared" si="3"/>
-        <v>23437.299999999988</v>
-      </c>
-      <c r="E19" s="17">
+        <v>94064.1</v>
+      </c>
+      <c r="D19" s="21">
         <f t="shared" si="2"/>
-        <v>81564.100000000006</v>
-      </c>
-      <c r="F19" s="17">
-        <f t="shared" si="4"/>
+        <v>12158.600000000006</v>
+      </c>
+      <c r="E19" s="21">
+        <f>MAX($D$6:D19)</f>
         <v>12158.600000000006</v>
       </c>
     </row>
@@ -2678,20 +2806,16 @@
         <f t="shared" si="0"/>
         <v>4784.8500000000004</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="21">
         <f t="shared" si="1"/>
-        <v>178460.6</v>
-      </c>
-      <c r="D20" s="17">
-        <f t="shared" si="3"/>
-        <v>26772.300000000017</v>
-      </c>
-      <c r="E20" s="17">
+        <v>107890.3</v>
+      </c>
+      <c r="D20" s="21">
         <f t="shared" si="2"/>
-        <v>95390.3</v>
-      </c>
-      <c r="F20" s="17">
-        <f t="shared" si="4"/>
+        <v>13826.199999999997</v>
+      </c>
+      <c r="E20" s="21">
+        <f>MAX($D$6:D20)</f>
         <v>13826.199999999997</v>
       </c>
     </row>
@@ -2703,20 +2827,16 @@
         <f t="shared" si="0"/>
         <v>5639.2833333333338</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="21">
         <f t="shared" si="1"/>
-        <v>209008.4</v>
-      </c>
-      <c r="D21" s="17">
-        <f t="shared" si="3"/>
-        <v>30547.799999999988</v>
-      </c>
-      <c r="E21" s="17">
+        <v>123604.2</v>
+      </c>
+      <c r="D21" s="21">
         <f t="shared" si="2"/>
-        <v>111104.2</v>
-      </c>
-      <c r="F21" s="17">
-        <f t="shared" si="4"/>
+        <v>15713.899999999994</v>
+      </c>
+      <c r="E21" s="21">
+        <f>MAX($D$6:D21)</f>
         <v>15713.899999999994</v>
       </c>
     </row>
@@ -2728,20 +2848,16 @@
         <f t="shared" si="0"/>
         <v>6616.7666666666664</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="21">
         <f t="shared" si="1"/>
-        <v>243828.8</v>
-      </c>
-      <c r="D22" s="17">
-        <f t="shared" si="3"/>
-        <v>34820.399999999994</v>
-      </c>
-      <c r="E22" s="17">
+        <v>141454.39999999999</v>
+      </c>
+      <c r="D22" s="21">
         <f t="shared" si="2"/>
-        <v>128954.4</v>
-      </c>
-      <c r="F22" s="17">
-        <f t="shared" si="4"/>
+        <v>17850.199999999997</v>
+      </c>
+      <c r="E22" s="21">
+        <f>MAX($D$6:D22)</f>
         <v>17850.199999999997</v>
       </c>
     </row>
@@ -2753,20 +2869,16 @@
         <f t="shared" si="0"/>
         <v>7733.333333333333</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="21">
         <f t="shared" si="1"/>
-        <v>283478.5</v>
-      </c>
-      <c r="D23" s="17">
-        <f t="shared" si="3"/>
-        <v>39649.700000000012</v>
-      </c>
-      <c r="E23" s="17">
+        <v>161719.29999999999</v>
+      </c>
+      <c r="D23" s="21">
         <f t="shared" si="2"/>
-        <v>149219.29999999999</v>
-      </c>
-      <c r="F23" s="17">
-        <f t="shared" si="4"/>
+        <v>20264.899999999994</v>
+      </c>
+      <c r="E23" s="21">
+        <f>MAX($D$6:D23)</f>
         <v>20264.899999999994</v>
       </c>
     </row>
@@ -2778,20 +2890,16 @@
         <f t="shared" si="0"/>
         <v>9007.0666666666675</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="21">
         <f t="shared" si="1"/>
-        <v>328585.40000000002</v>
-      </c>
-      <c r="D24" s="17">
-        <f t="shared" si="3"/>
-        <v>45106.900000000023</v>
-      </c>
-      <c r="E24" s="17">
+        <v>184712.7</v>
+      </c>
+      <c r="D24" s="21">
         <f t="shared" si="2"/>
-        <v>172212.7</v>
-      </c>
-      <c r="F24" s="17">
-        <f t="shared" si="4"/>
+        <v>22993.400000000023</v>
+      </c>
+      <c r="E24" s="21">
+        <f>MAX($D$6:D24)</f>
         <v>22993.400000000023</v>
       </c>
     </row>
@@ -2803,20 +2911,16 @@
         <f t="shared" si="0"/>
         <v>10458.200000000001</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="21">
         <f t="shared" si="1"/>
-        <v>379851.9</v>
-      </c>
-      <c r="D25" s="17">
-        <f t="shared" si="3"/>
-        <v>51266.5</v>
-      </c>
-      <c r="E25" s="17">
+        <v>210786</v>
+      </c>
+      <c r="D25" s="21">
         <f t="shared" si="2"/>
-        <v>198286</v>
-      </c>
-      <c r="F25" s="17">
-        <f t="shared" si="4"/>
+        <v>26073.299999999988</v>
+      </c>
+      <c r="E25" s="21">
+        <f>MAX($D$6:D25)</f>
         <v>26073.299999999988</v>
       </c>
     </row>
@@ -2828,66 +2932,56 @@
         <f t="shared" si="0"/>
         <v>12109.5</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="21">
         <f t="shared" si="1"/>
-        <v>438068.8</v>
-      </c>
-      <c r="D26" s="17">
-        <f t="shared" si="3"/>
-        <v>58216.899999999965</v>
-      </c>
-      <c r="E26" s="17">
+        <v>240334.4</v>
+      </c>
+      <c r="D26" s="21">
         <f t="shared" si="2"/>
-        <v>227834.4</v>
-      </c>
-      <c r="F26" s="17">
-        <f t="shared" si="4"/>
         <v>29548.399999999994</v>
       </c>
+      <c r="E26" s="21">
+        <f>MAX($D$6:D26)</f>
+        <v>29548.399999999994</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="25">
-        <f>SUMPRODUCT(MAX((D6:D26&lt;=TOM_PRICE)*A6:A26))</f>
-        <v>5</v>
-      </c>
-      <c r="F27" s="25">
-        <f>SUMPRODUCT(MAX((F6:F26&lt;=TOM_PRICE)*A6:A26))</f>
+      <c r="A27" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="28">
+        <f>SUMPRODUCT((E6:E26&lt;=TOM_PRICE)*1)-1</f>
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
+      <c r="A29" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2895,21 +2989,18 @@
         <v>0</v>
       </c>
       <c r="B31" s="15">
-        <f t="shared" ref="B31:B51" si="5">ROUND(A31*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A31*60,0)/60</f>
+        <f t="shared" ref="B31:B51" si="3">ROUND(A31*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A31*60,0)/60</f>
         <v>0</v>
       </c>
-      <c r="C31" s="17">
-        <f t="shared" ref="C31:C51" si="6">ROUND(B31*FARMER_RATE+A31*CAR_FERT_COST,1)</f>
+      <c r="C31" s="21">
+        <f t="shared" ref="C31:C51" si="4">ROUND(IF(B31&lt;=FARMER_HRS_CAP,B31*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B31-FARMER_HRS_CAP)*TEMP_RATE)+A31*CAR_FERT_COST,1)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="21">
         <v>0</v>
       </c>
-      <c r="E31" s="17">
-        <f t="shared" ref="E31:E51" si="7">ROUND(B31*TEMP_RATE+A31*CAR_FERT_COST,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="17">
+      <c r="E31" s="21">
+        <f>MAX($D$31:D31)</f>
         <v>0</v>
       </c>
     </row>
@@ -2918,424 +3009,356 @@
         <v>1</v>
       </c>
       <c r="B32" s="15">
-        <f t="shared" si="5"/>
-        <v>30.733333333333334</v>
-      </c>
-      <c r="C32" s="17">
-        <f t="shared" si="6"/>
-        <v>1507.1</v>
-      </c>
-      <c r="D32" s="17">
-        <f t="shared" ref="D32:D51" si="8">C32-C31</f>
-        <v>1507.1</v>
-      </c>
-      <c r="E32" s="17">
-        <f t="shared" si="7"/>
-        <v>973.6</v>
-      </c>
-      <c r="F32" s="17">
-        <f t="shared" ref="F32:F51" si="9">E32-E31</f>
-        <v>973.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="3"/>
+        <v>30.75</v>
+      </c>
+      <c r="C32" s="21">
+        <f t="shared" si="4"/>
+        <v>1507.7</v>
+      </c>
+      <c r="D32" s="21">
+        <f t="shared" ref="D32:D51" si="5">C32-C31</f>
+        <v>1507.7</v>
+      </c>
+      <c r="E32" s="21">
+        <f>MAX($D$31:D32)</f>
+        <v>1507.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5">
         <v>2</v>
       </c>
       <c r="B33" s="15">
+        <f t="shared" si="3"/>
+        <v>63.033333333333331</v>
+      </c>
+      <c r="C33" s="21">
+        <f t="shared" si="4"/>
+        <v>3068.7</v>
+      </c>
+      <c r="D33" s="21">
         <f t="shared" si="5"/>
-        <v>63.016666666666666</v>
-      </c>
-      <c r="C33" s="17">
-        <f t="shared" si="6"/>
-        <v>3068.1</v>
-      </c>
-      <c r="D33" s="17">
-        <f t="shared" si="8"/>
-        <v>1561</v>
-      </c>
-      <c r="E33" s="17">
-        <f t="shared" si="7"/>
-        <v>1974</v>
-      </c>
-      <c r="F33" s="17">
-        <f t="shared" si="9"/>
-        <v>1000.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1560.9999999999998</v>
+      </c>
+      <c r="E33" s="21">
+        <f>MAX($D$31:D33)</f>
+        <v>1560.9999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5">
         <v>3</v>
       </c>
       <c r="B34" s="15">
+        <f t="shared" si="3"/>
+        <v>96.916666666666671</v>
+      </c>
+      <c r="C34" s="21">
+        <f t="shared" si="4"/>
+        <v>4685.2</v>
+      </c>
+      <c r="D34" s="21">
         <f t="shared" si="5"/>
-        <v>96.88333333333334</v>
-      </c>
-      <c r="C34" s="17">
-        <f t="shared" si="6"/>
-        <v>4684</v>
-      </c>
-      <c r="D34" s="17">
-        <f t="shared" si="8"/>
-        <v>1615.9</v>
-      </c>
-      <c r="E34" s="17">
-        <f t="shared" si="7"/>
-        <v>3002</v>
-      </c>
-      <c r="F34" s="17">
-        <f t="shared" si="9"/>
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1616.5</v>
+      </c>
+      <c r="E34" s="21">
+        <f>MAX($D$31:D34)</f>
+        <v>1616.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5">
         <v>4</v>
       </c>
       <c r="B35" s="15">
+        <f t="shared" si="3"/>
+        <v>132.44999999999999</v>
+      </c>
+      <c r="C35" s="21">
+        <f t="shared" si="4"/>
+        <v>6359</v>
+      </c>
+      <c r="D35" s="21">
         <f t="shared" si="5"/>
-        <v>132.4</v>
-      </c>
-      <c r="C35" s="17">
-        <f t="shared" si="6"/>
-        <v>6357.2</v>
-      </c>
-      <c r="D35" s="17">
-        <f t="shared" si="8"/>
-        <v>1673.1999999999998</v>
-      </c>
-      <c r="E35" s="17">
-        <f t="shared" si="7"/>
-        <v>4058.6</v>
-      </c>
-      <c r="F35" s="17">
-        <f t="shared" si="9"/>
-        <v>1056.5999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1673.8000000000002</v>
+      </c>
+      <c r="E35" s="21">
+        <f>MAX($D$31:D35)</f>
+        <v>1673.8000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5">
         <v>5</v>
       </c>
       <c r="B36" s="15">
+        <f t="shared" si="3"/>
+        <v>169.71666666666667</v>
+      </c>
+      <c r="C36" s="21">
+        <f t="shared" si="4"/>
+        <v>8092.9</v>
+      </c>
+      <c r="D36" s="21">
         <f t="shared" si="5"/>
-        <v>169.65</v>
-      </c>
-      <c r="C36" s="17">
-        <f t="shared" si="6"/>
-        <v>8090.6</v>
-      </c>
-      <c r="D36" s="17">
-        <f t="shared" si="8"/>
-        <v>1733.4000000000005</v>
-      </c>
-      <c r="E36" s="17">
-        <f t="shared" si="7"/>
-        <v>5145.3</v>
-      </c>
-      <c r="F36" s="17">
-        <f t="shared" si="9"/>
-        <v>1086.7000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1733.8999999999996</v>
+      </c>
+      <c r="E36" s="21">
+        <f>MAX($D$31:D36)</f>
+        <v>1733.8999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5">
         <v>6</v>
       </c>
       <c r="B37" s="15">
+        <f t="shared" si="3"/>
+        <v>208.75</v>
+      </c>
+      <c r="C37" s="21">
+        <f t="shared" si="4"/>
+        <v>9888.2999999999993</v>
+      </c>
+      <c r="D37" s="21">
         <f t="shared" si="5"/>
-        <v>208.66666666666666</v>
-      </c>
-      <c r="C37" s="17">
-        <f t="shared" si="6"/>
-        <v>9885.4</v>
-      </c>
-      <c r="D37" s="17">
-        <f t="shared" si="8"/>
-        <v>1794.7999999999993</v>
-      </c>
-      <c r="E37" s="17">
-        <f t="shared" si="7"/>
-        <v>6262.7</v>
-      </c>
-      <c r="F37" s="17">
-        <f t="shared" si="9"/>
-        <v>1117.3999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1795.3999999999996</v>
+      </c>
+      <c r="E37" s="21">
+        <f>MAX($D$31:D37)</f>
+        <v>1795.3999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="5">
         <v>7</v>
       </c>
       <c r="B38" s="15">
+        <f t="shared" si="3"/>
+        <v>249.61666666666667</v>
+      </c>
+      <c r="C38" s="21">
+        <f t="shared" si="4"/>
+        <v>11747.2</v>
+      </c>
+      <c r="D38" s="21">
         <f t="shared" si="5"/>
-        <v>249.51666666666668</v>
-      </c>
-      <c r="C38" s="17">
-        <f t="shared" si="6"/>
-        <v>11743.8</v>
-      </c>
-      <c r="D38" s="17">
-        <f t="shared" si="8"/>
-        <v>1858.3999999999996</v>
-      </c>
-      <c r="E38" s="17">
-        <f t="shared" si="7"/>
-        <v>7411.9</v>
-      </c>
-      <c r="F38" s="17">
-        <f t="shared" si="9"/>
-        <v>1149.1999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1858.9000000000015</v>
+      </c>
+      <c r="E38" s="21">
+        <f>MAX($D$31:D38)</f>
+        <v>1858.9000000000015</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5">
         <v>8</v>
       </c>
       <c r="B39" s="15">
+        <f t="shared" si="3"/>
+        <v>292.41666666666669</v>
+      </c>
+      <c r="C39" s="21">
+        <f t="shared" si="4"/>
+        <v>13673.4</v>
+      </c>
+      <c r="D39" s="21">
         <f t="shared" si="5"/>
-        <v>292.3</v>
-      </c>
-      <c r="C39" s="17">
-        <f t="shared" si="6"/>
-        <v>13669.3</v>
-      </c>
-      <c r="D39" s="17">
-        <f t="shared" si="8"/>
-        <v>1925.5</v>
-      </c>
-      <c r="E39" s="17">
-        <f t="shared" si="7"/>
-        <v>8594.7000000000007</v>
-      </c>
-      <c r="F39" s="17">
-        <f t="shared" si="9"/>
-        <v>1182.8000000000011</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1926.1999999999989</v>
+      </c>
+      <c r="E39" s="21">
+        <f>MAX($D$31:D39)</f>
+        <v>1926.1999999999989</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5">
         <v>9</v>
       </c>
       <c r="B40" s="15">
+        <f t="shared" si="3"/>
+        <v>337.2</v>
+      </c>
+      <c r="C40" s="21">
+        <f t="shared" si="4"/>
+        <v>15668.3</v>
+      </c>
+      <c r="D40" s="21">
         <f t="shared" si="5"/>
-        <v>337.05</v>
-      </c>
-      <c r="C40" s="17">
-        <f t="shared" si="6"/>
-        <v>15663.1</v>
-      </c>
-      <c r="D40" s="17">
-        <f t="shared" si="8"/>
-        <v>1993.8000000000011</v>
-      </c>
-      <c r="E40" s="17">
-        <f t="shared" si="7"/>
-        <v>9811.6</v>
-      </c>
-      <c r="F40" s="17">
-        <f t="shared" si="9"/>
-        <v>1216.8999999999996</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>1994.8999999999996</v>
+      </c>
+      <c r="E40" s="21">
+        <f>MAX($D$31:D40)</f>
+        <v>1994.8999999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5">
         <v>10</v>
       </c>
       <c r="B41" s="15">
+        <f t="shared" si="3"/>
+        <v>384.03333333333336</v>
+      </c>
+      <c r="C41" s="21">
+        <f t="shared" si="4"/>
+        <v>17734.5</v>
+      </c>
+      <c r="D41" s="21">
         <f t="shared" si="5"/>
-        <v>383.86666666666667</v>
-      </c>
-      <c r="C41" s="17">
-        <f t="shared" si="6"/>
-        <v>17728.7</v>
-      </c>
-      <c r="D41" s="17">
-        <f t="shared" si="8"/>
-        <v>2065.6000000000004</v>
-      </c>
-      <c r="E41" s="17">
-        <f t="shared" si="7"/>
-        <v>11064.4</v>
-      </c>
-      <c r="F41" s="17">
-        <f t="shared" si="9"/>
-        <v>1252.7999999999993</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2066.2000000000007</v>
+      </c>
+      <c r="E41" s="21">
+        <f>MAX($D$31:D41)</f>
+        <v>2066.2000000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5">
         <v>11</v>
       </c>
       <c r="B42" s="15">
+        <f t="shared" si="3"/>
+        <v>432.98333333333335</v>
+      </c>
+      <c r="C42" s="21">
+        <f t="shared" si="4"/>
+        <v>19874.099999999999</v>
+      </c>
+      <c r="D42" s="21">
         <f t="shared" si="5"/>
-        <v>432.81666666666666</v>
-      </c>
-      <c r="C42" s="17">
-        <f t="shared" si="6"/>
-        <v>19868.400000000001</v>
-      </c>
-      <c r="D42" s="17">
-        <f t="shared" si="8"/>
-        <v>2139.7000000000007</v>
-      </c>
-      <c r="E42" s="17">
-        <f t="shared" si="7"/>
-        <v>12354.2</v>
-      </c>
-      <c r="F42" s="17">
-        <f t="shared" si="9"/>
-        <v>1289.8000000000011</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2139.5999999999985</v>
+      </c>
+      <c r="E42" s="21">
+        <f>MAX($D$31:D42)</f>
+        <v>2139.5999999999985</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5">
         <v>12</v>
       </c>
       <c r="B43" s="15">
+        <f t="shared" si="3"/>
+        <v>484.16666666666669</v>
+      </c>
+      <c r="C43" s="21">
+        <f t="shared" si="4"/>
+        <v>22091.3</v>
+      </c>
+      <c r="D43" s="21">
         <f t="shared" si="5"/>
-        <v>483.96666666666664</v>
-      </c>
-      <c r="C43" s="17">
-        <f t="shared" si="6"/>
-        <v>22084.400000000001</v>
-      </c>
-      <c r="D43" s="17">
-        <f t="shared" si="8"/>
-        <v>2216</v>
-      </c>
-      <c r="E43" s="17">
-        <f t="shared" si="7"/>
-        <v>13682.2</v>
-      </c>
-      <c r="F43" s="17">
-        <f t="shared" si="9"/>
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2217.2000000000007</v>
+      </c>
+      <c r="E43" s="21">
+        <f>MAX($D$31:D43)</f>
+        <v>2217.2000000000007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5">
         <v>13</v>
       </c>
       <c r="B44" s="15">
+        <f t="shared" si="3"/>
+        <v>537.61666666666667</v>
+      </c>
+      <c r="C44" s="21">
+        <f t="shared" si="4"/>
+        <v>24387.200000000001</v>
+      </c>
+      <c r="D44" s="21">
         <f t="shared" si="5"/>
-        <v>537.4</v>
-      </c>
-      <c r="C44" s="17">
-        <f t="shared" si="6"/>
-        <v>24379.7</v>
-      </c>
-      <c r="D44" s="17">
-        <f t="shared" si="8"/>
-        <v>2295.2999999999993</v>
-      </c>
-      <c r="E44" s="17">
-        <f t="shared" si="7"/>
-        <v>15049.9</v>
-      </c>
-      <c r="F44" s="17">
-        <f t="shared" si="9"/>
-        <v>1367.6999999999989</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2295.9000000000015</v>
+      </c>
+      <c r="E44" s="21">
+        <f>MAX($D$31:D44)</f>
+        <v>2295.9000000000015</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5">
         <v>14</v>
       </c>
       <c r="B45" s="15">
+        <f t="shared" si="3"/>
+        <v>593.45000000000005</v>
+      </c>
+      <c r="C45" s="21">
+        <f t="shared" si="4"/>
+        <v>26765.9</v>
+      </c>
+      <c r="D45" s="21">
         <f t="shared" si="5"/>
-        <v>593.2166666666667</v>
-      </c>
-      <c r="C45" s="17">
-        <f t="shared" si="6"/>
-        <v>26757.8</v>
-      </c>
-      <c r="D45" s="17">
-        <f t="shared" si="8"/>
-        <v>2378.0999999999985</v>
-      </c>
-      <c r="E45" s="17">
-        <f t="shared" si="7"/>
-        <v>16458.900000000001</v>
-      </c>
-      <c r="F45" s="17">
-        <f t="shared" si="9"/>
-        <v>1409.0000000000018</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2378.7000000000007</v>
+      </c>
+      <c r="E45" s="21">
+        <f>MAX($D$31:D45)</f>
+        <v>2378.7000000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5">
         <v>15</v>
       </c>
       <c r="B46" s="15">
+        <f t="shared" si="3"/>
+        <v>651.73333333333335</v>
+      </c>
+      <c r="C46" s="21">
+        <f t="shared" si="4"/>
+        <v>29229.599999999999</v>
+      </c>
+      <c r="D46" s="21">
         <f t="shared" si="5"/>
-        <v>651.4666666666667</v>
-      </c>
-      <c r="C46" s="17">
-        <f t="shared" si="6"/>
-        <v>29220.400000000001</v>
-      </c>
-      <c r="D46" s="17">
-        <f t="shared" si="8"/>
-        <v>2462.6000000000022</v>
-      </c>
-      <c r="E46" s="17">
-        <f t="shared" si="7"/>
-        <v>17910.2</v>
-      </c>
-      <c r="F46" s="17">
-        <f t="shared" si="9"/>
-        <v>1451.2999999999993</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2463.6999999999971</v>
+      </c>
+      <c r="E46" s="21">
+        <f>MAX($D$31:D46)</f>
+        <v>2463.6999999999971</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="5">
         <v>16</v>
       </c>
       <c r="B47" s="15">
+        <f t="shared" si="3"/>
+        <v>712.56666666666672</v>
+      </c>
+      <c r="C47" s="21">
+        <f t="shared" si="4"/>
+        <v>31781.9</v>
+      </c>
+      <c r="D47" s="21">
         <f t="shared" si="5"/>
-        <v>712.2833333333333</v>
-      </c>
-      <c r="C47" s="17">
-        <f t="shared" si="6"/>
-        <v>31772.1</v>
-      </c>
-      <c r="D47" s="17">
-        <f t="shared" si="8"/>
-        <v>2551.6999999999971</v>
-      </c>
-      <c r="E47" s="17">
-        <f t="shared" si="7"/>
-        <v>19406</v>
-      </c>
-      <c r="F47" s="17">
-        <f t="shared" si="9"/>
-        <v>1495.7999999999993</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>2552.3000000000029</v>
+      </c>
+      <c r="E47" s="21">
+        <f>MAX($D$31:D47)</f>
+        <v>2552.3000000000029</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5">
         <v>17</v>
       </c>
       <c r="B48" s="15">
+        <f t="shared" si="3"/>
+        <v>776.0333333333333</v>
+      </c>
+      <c r="C48" s="21">
+        <f t="shared" si="4"/>
+        <v>33452.800000000003</v>
+      </c>
+      <c r="D48" s="21">
         <f t="shared" si="5"/>
-        <v>775.7166666666667</v>
-      </c>
-      <c r="C48" s="17">
-        <f t="shared" si="6"/>
-        <v>34414.6</v>
-      </c>
-      <c r="D48" s="17">
-        <f t="shared" si="8"/>
-        <v>2642.5</v>
-      </c>
-      <c r="E48" s="17">
-        <f t="shared" si="7"/>
-        <v>20947.3</v>
-      </c>
-      <c r="F48" s="17">
-        <f t="shared" si="9"/>
-        <v>1541.2999999999993</v>
+        <v>1670.9000000000015</v>
+      </c>
+      <c r="E48" s="21">
+        <f>MAX($D$31:D48)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3343,24 +3366,20 @@
         <v>18</v>
       </c>
       <c r="B49" s="15">
+        <f t="shared" si="3"/>
+        <v>842.2166666666667</v>
+      </c>
+      <c r="C49" s="21">
+        <f t="shared" si="4"/>
+        <v>35041.800000000003</v>
+      </c>
+      <c r="D49" s="21">
         <f t="shared" si="5"/>
-        <v>841.88333333333333</v>
-      </c>
-      <c r="C49" s="17">
-        <f t="shared" si="6"/>
-        <v>37152.1</v>
-      </c>
-      <c r="D49" s="17">
-        <f t="shared" si="8"/>
-        <v>2737.5</v>
-      </c>
-      <c r="E49" s="17">
-        <f t="shared" si="7"/>
-        <v>22536</v>
-      </c>
-      <c r="F49" s="17">
-        <f t="shared" si="9"/>
-        <v>1588.7000000000007</v>
+        <v>1589</v>
+      </c>
+      <c r="E49" s="21">
+        <f>MAX($D$31:D49)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3368,24 +3387,20 @@
         <v>19</v>
       </c>
       <c r="B50" s="15">
+        <f t="shared" si="3"/>
+        <v>911.23333333333335</v>
+      </c>
+      <c r="C50" s="21">
+        <f t="shared" si="4"/>
+        <v>36680</v>
+      </c>
+      <c r="D50" s="21">
         <f t="shared" si="5"/>
-        <v>910.86666666666667</v>
-      </c>
-      <c r="C50" s="17">
-        <f t="shared" si="6"/>
-        <v>39987.300000000003</v>
-      </c>
-      <c r="D50" s="17">
-        <f t="shared" si="8"/>
-        <v>2835.2000000000044</v>
-      </c>
-      <c r="E50" s="17">
-        <f t="shared" si="7"/>
-        <v>24173.7</v>
-      </c>
-      <c r="F50" s="17">
-        <f t="shared" si="9"/>
-        <v>1637.7000000000007</v>
+        <v>1638.1999999999971</v>
+      </c>
+      <c r="E50" s="21">
+        <f>MAX($D$31:D50)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3393,69 +3408,59 @@
         <v>20</v>
       </c>
       <c r="B51" s="15">
+        <f t="shared" si="3"/>
+        <v>983.16666666666663</v>
+      </c>
+      <c r="C51" s="21">
+        <f t="shared" si="4"/>
+        <v>38368.9</v>
+      </c>
+      <c r="D51" s="21">
         <f t="shared" si="5"/>
-        <v>982.7833333333333</v>
-      </c>
-      <c r="C51" s="17">
-        <f t="shared" si="6"/>
-        <v>42924.4</v>
-      </c>
-      <c r="D51" s="17">
-        <f t="shared" si="8"/>
-        <v>2937.0999999999985</v>
-      </c>
-      <c r="E51" s="17">
-        <f t="shared" si="7"/>
-        <v>25862.2</v>
-      </c>
-      <c r="F51" s="17">
-        <f t="shared" si="9"/>
-        <v>1688.5</v>
+        <v>1688.9000000000015</v>
+      </c>
+      <c r="E51" s="21">
+        <f>MAX($D$31:D51)</f>
+        <v>2552.3000000000029</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" s="25">
-        <f>SUMPRODUCT(MAX((D31:D51&lt;=CAR_PRICE)*A31:A51))</f>
+      <c r="A52" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" s="28">
+        <f>SUMPRODUCT((E31:E51&lt;=CAR_PRICE)*1)-1</f>
         <v>10</v>
       </c>
-      <c r="F52" s="25">
-        <f>SUMPRODUCT(MAX((F31:F51&lt;=CAR_PRICE)*A31:A51))</f>
-        <v>20</v>
-      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
+      <c r="A54" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>140</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3463,21 +3468,18 @@
         <v>0</v>
       </c>
       <c r="B56" s="15">
-        <f t="shared" ref="B56:B86" si="10">ROUND(A56*MES_HRS*WEEKS*(1+MES_DIM_PCT)^A56*60,0)/60</f>
+        <f t="shared" ref="B56:B86" si="6">ROUND(A56*MES_HRS*WEEKS*(1+MES_DIM_PCT)^A56*60,0)/60</f>
         <v>0</v>
       </c>
-      <c r="C56" s="17">
-        <f t="shared" ref="C56:C86" si="11">ROUND(B56*FARMER_RATE+A56*MES_FERT_COST,1)</f>
+      <c r="C56" s="21">
+        <f t="shared" ref="C56:C86" si="7">ROUND(IF(B56&lt;=FARMER_HRS_CAP,B56*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B56-FARMER_HRS_CAP)*TEMP_RATE)+A56*MES_FERT_COST,1)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="21">
         <v>0</v>
       </c>
-      <c r="E56" s="17">
-        <f t="shared" ref="E56:E86" si="12">ROUND(B56*TEMP_RATE+A56*MES_FERT_COST,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="17">
+      <c r="E56" s="21">
+        <f>MAX($D$56:D56)</f>
         <v>0</v>
       </c>
     </row>
@@ -3486,24 +3488,20 @@
         <v>1</v>
       </c>
       <c r="B57" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>45.56666666666667</v>
       </c>
-      <c r="C57" s="17">
-        <f t="shared" si="11"/>
+      <c r="C57" s="21">
+        <f t="shared" si="7"/>
         <v>2462.1999999999998</v>
       </c>
-      <c r="D57" s="17">
-        <f t="shared" ref="D57:D86" si="13">C57-C56</f>
+      <c r="D57" s="21">
+        <f t="shared" ref="D57:D86" si="8">C57-C56</f>
         <v>2462.1999999999998</v>
       </c>
-      <c r="E57" s="17">
-        <f t="shared" si="12"/>
-        <v>1671.1</v>
-      </c>
-      <c r="F57" s="17">
-        <f t="shared" ref="F57:F86" si="14">E57-E56</f>
-        <v>1671.1</v>
+      <c r="E57" s="21">
+        <f>MAX($D$56:D57)</f>
+        <v>2462.1999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3511,24 +3509,20 @@
         <v>2</v>
       </c>
       <c r="B58" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>92.266666666666666</v>
       </c>
-      <c r="C58" s="17">
-        <f t="shared" si="11"/>
+      <c r="C58" s="21">
+        <f t="shared" si="7"/>
         <v>4963.7</v>
       </c>
-      <c r="D58" s="17">
-        <f t="shared" si="13"/>
+      <c r="D58" s="21">
+        <f t="shared" si="8"/>
         <v>2501.5</v>
       </c>
-      <c r="E58" s="17">
-        <f t="shared" si="12"/>
-        <v>3361.9</v>
-      </c>
-      <c r="F58" s="17">
-        <f t="shared" si="14"/>
-        <v>1690.8000000000002</v>
+      <c r="E58" s="21">
+        <f>MAX($D$56:D58)</f>
+        <v>2501.5</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3536,24 +3530,20 @@
         <v>3</v>
       </c>
       <c r="B59" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>140.13333333333333</v>
       </c>
-      <c r="C59" s="17">
-        <f t="shared" si="11"/>
+      <c r="C59" s="21">
+        <f t="shared" si="7"/>
         <v>7505.7</v>
       </c>
-      <c r="D59" s="17">
-        <f t="shared" si="13"/>
+      <c r="D59" s="21">
+        <f t="shared" si="8"/>
         <v>2542</v>
       </c>
-      <c r="E59" s="17">
-        <f t="shared" si="12"/>
-        <v>5072.8999999999996</v>
-      </c>
-      <c r="F59" s="17">
-        <f t="shared" si="14"/>
-        <v>1710.9999999999995</v>
+      <c r="E59" s="21">
+        <f>MAX($D$56:D59)</f>
+        <v>2542</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3561,24 +3551,20 @@
         <v>4</v>
       </c>
       <c r="B60" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>189.16666666666666</v>
       </c>
-      <c r="C60" s="17">
-        <f t="shared" si="11"/>
+      <c r="C60" s="21">
+        <f t="shared" si="7"/>
         <v>10088.299999999999</v>
       </c>
-      <c r="D60" s="17">
-        <f t="shared" si="13"/>
+      <c r="D60" s="21">
+        <f t="shared" si="8"/>
         <v>2582.5999999999995</v>
       </c>
-      <c r="E60" s="17">
-        <f t="shared" si="12"/>
-        <v>6804.1</v>
-      </c>
-      <c r="F60" s="17">
-        <f t="shared" si="14"/>
-        <v>1731.2000000000007</v>
+      <c r="E60" s="21">
+        <f>MAX($D$56:D60)</f>
+        <v>2582.5999999999995</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3586,24 +3572,20 @@
         <v>5</v>
       </c>
       <c r="B61" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>239.41666666666666</v>
       </c>
-      <c r="C61" s="17">
-        <f t="shared" si="11"/>
+      <c r="C61" s="21">
+        <f t="shared" si="7"/>
         <v>12713.1</v>
       </c>
-      <c r="D61" s="17">
-        <f t="shared" si="13"/>
+      <c r="D61" s="21">
+        <f t="shared" si="8"/>
         <v>2624.8000000000011</v>
       </c>
-      <c r="E61" s="17">
-        <f t="shared" si="12"/>
-        <v>8556.5</v>
-      </c>
-      <c r="F61" s="17">
-        <f t="shared" si="14"/>
-        <v>1752.3999999999996</v>
+      <c r="E61" s="21">
+        <f>MAX($D$56:D61)</f>
+        <v>2624.8000000000011</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3611,24 +3593,20 @@
         <v>6</v>
       </c>
       <c r="B62" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>290.89999999999998</v>
       </c>
-      <c r="C62" s="17">
-        <f t="shared" si="11"/>
+      <c r="C62" s="21">
+        <f t="shared" si="7"/>
         <v>15380.7</v>
       </c>
-      <c r="D62" s="17">
-        <f t="shared" si="13"/>
+      <c r="D62" s="21">
+        <f t="shared" si="8"/>
         <v>2667.6000000000004</v>
       </c>
-      <c r="E62" s="17">
-        <f t="shared" si="12"/>
-        <v>10330.299999999999</v>
-      </c>
-      <c r="F62" s="17">
-        <f t="shared" si="14"/>
-        <v>1773.7999999999993</v>
+      <c r="E62" s="21">
+        <f>MAX($D$56:D62)</f>
+        <v>2667.6000000000004</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3636,24 +3614,20 @@
         <v>7</v>
       </c>
       <c r="B63" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>343.61666666666667</v>
       </c>
-      <c r="C63" s="17">
-        <f t="shared" si="11"/>
+      <c r="C63" s="21">
+        <f t="shared" si="7"/>
         <v>18091.099999999999</v>
       </c>
-      <c r="D63" s="17">
-        <f t="shared" si="13"/>
+      <c r="D63" s="21">
+        <f t="shared" si="8"/>
         <v>2710.3999999999978</v>
       </c>
-      <c r="E63" s="17">
-        <f t="shared" si="12"/>
-        <v>12125.6</v>
-      </c>
-      <c r="F63" s="17">
-        <f t="shared" si="14"/>
-        <v>1795.3000000000011</v>
+      <c r="E63" s="21">
+        <f>MAX($D$56:D63)</f>
+        <v>2710.3999999999978</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -3661,599 +3635,500 @@
         <v>8</v>
       </c>
       <c r="B64" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>397.61666666666667</v>
       </c>
-      <c r="C64" s="17">
-        <f t="shared" si="11"/>
+      <c r="C64" s="21">
+        <f t="shared" si="7"/>
         <v>20846.099999999999</v>
       </c>
-      <c r="D64" s="17">
-        <f t="shared" si="13"/>
+      <c r="D64" s="21">
+        <f t="shared" si="8"/>
         <v>2755</v>
       </c>
-      <c r="E64" s="17">
-        <f t="shared" si="12"/>
-        <v>13943.1</v>
-      </c>
-      <c r="F64" s="17">
-        <f t="shared" si="14"/>
-        <v>1817.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E64" s="21">
+        <f>MAX($D$56:D64)</f>
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5">
         <v>9</v>
       </c>
       <c r="B65" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>452.9</v>
       </c>
-      <c r="C65" s="17">
-        <f t="shared" si="11"/>
+      <c r="C65" s="21">
+        <f t="shared" si="7"/>
         <v>23645.7</v>
       </c>
-      <c r="D65" s="17">
-        <f t="shared" si="13"/>
+      <c r="D65" s="21">
+        <f t="shared" si="8"/>
         <v>2799.6000000000022</v>
       </c>
-      <c r="E65" s="17">
-        <f t="shared" si="12"/>
-        <v>15782.8</v>
-      </c>
-      <c r="F65" s="17">
-        <f t="shared" si="14"/>
-        <v>1839.6999999999989</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E65" s="21">
+        <f>MAX($D$56:D65)</f>
+        <v>2799.6000000000022</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5">
         <v>10</v>
       </c>
       <c r="B66" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>509.51666666666665</v>
       </c>
-      <c r="C66" s="17">
-        <f t="shared" si="11"/>
+      <c r="C66" s="21">
+        <f t="shared" si="7"/>
         <v>26491.599999999999</v>
       </c>
-      <c r="D66" s="17">
-        <f t="shared" si="13"/>
+      <c r="D66" s="21">
+        <f t="shared" si="8"/>
         <v>2845.8999999999978</v>
       </c>
-      <c r="E66" s="17">
-        <f t="shared" si="12"/>
-        <v>17645.8</v>
-      </c>
-      <c r="F66" s="17">
-        <f t="shared" si="14"/>
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E66" s="21">
+        <f>MAX($D$56:D66)</f>
+        <v>2845.8999999999978</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5">
         <v>11</v>
       </c>
       <c r="B67" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>567.48333333333335</v>
       </c>
-      <c r="C67" s="17">
-        <f t="shared" si="11"/>
+      <c r="C67" s="21">
+        <f t="shared" si="7"/>
         <v>29384.3</v>
       </c>
-      <c r="D67" s="17">
-        <f t="shared" si="13"/>
+      <c r="D67" s="21">
+        <f t="shared" si="8"/>
         <v>2892.7000000000007</v>
       </c>
-      <c r="E67" s="17">
-        <f t="shared" si="12"/>
-        <v>19532.099999999999</v>
-      </c>
-      <c r="F67" s="17">
-        <f t="shared" si="14"/>
-        <v>1886.2999999999993</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E67" s="21">
+        <f>MAX($D$56:D67)</f>
+        <v>2892.7000000000007</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5">
         <v>12</v>
       </c>
       <c r="B68" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>626.79999999999995</v>
       </c>
-      <c r="C68" s="17">
-        <f t="shared" si="11"/>
+      <c r="C68" s="21">
+        <f t="shared" si="7"/>
         <v>32323.9</v>
       </c>
-      <c r="D68" s="17">
-        <f t="shared" si="13"/>
+      <c r="D68" s="21">
+        <f t="shared" si="8"/>
         <v>2939.6000000000022</v>
       </c>
-      <c r="E68" s="17">
-        <f t="shared" si="12"/>
-        <v>21441.9</v>
-      </c>
-      <c r="F68" s="17">
-        <f t="shared" si="14"/>
-        <v>1909.8000000000029</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E68" s="21">
+        <f>MAX($D$56:D68)</f>
+        <v>2939.6000000000022</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5">
         <v>13</v>
       </c>
       <c r="B69" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>687.5333333333333</v>
       </c>
-      <c r="C69" s="17">
-        <f t="shared" si="11"/>
+      <c r="C69" s="21">
+        <f t="shared" si="7"/>
         <v>35312.699999999997</v>
       </c>
-      <c r="D69" s="17">
-        <f t="shared" si="13"/>
+      <c r="D69" s="21">
+        <f t="shared" si="8"/>
         <v>2988.7999999999956</v>
       </c>
-      <c r="E69" s="17">
-        <f t="shared" si="12"/>
-        <v>23376.3</v>
-      </c>
-      <c r="F69" s="17">
-        <f t="shared" si="14"/>
-        <v>1934.3999999999978</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E69" s="21">
+        <f>MAX($D$56:D69)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5">
         <v>14</v>
       </c>
       <c r="B70" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>749.66666666666663</v>
       </c>
-      <c r="C70" s="17">
-        <f t="shared" si="11"/>
-        <v>38350.1</v>
-      </c>
-      <c r="D70" s="17">
-        <f t="shared" si="13"/>
-        <v>3037.4000000000015</v>
-      </c>
-      <c r="E70" s="17">
-        <f t="shared" si="12"/>
-        <v>25335</v>
-      </c>
-      <c r="F70" s="17">
-        <f t="shared" si="14"/>
-        <v>1958.7000000000007</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C70" s="21">
+        <f t="shared" si="7"/>
+        <v>37835</v>
+      </c>
+      <c r="D70" s="21">
+        <f t="shared" si="8"/>
+        <v>2522.3000000000029</v>
+      </c>
+      <c r="E70" s="21">
+        <f>MAX($D$56:D70)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5">
         <v>15</v>
       </c>
       <c r="B71" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>813.26666666666665</v>
       </c>
-      <c r="C71" s="17">
-        <f t="shared" si="11"/>
-        <v>41438.400000000001</v>
-      </c>
-      <c r="D71" s="17">
-        <f t="shared" si="13"/>
-        <v>3088.3000000000029</v>
-      </c>
-      <c r="E71" s="17">
-        <f t="shared" si="12"/>
-        <v>27319.200000000001</v>
-      </c>
-      <c r="F71" s="17">
-        <f t="shared" si="14"/>
-        <v>1984.2000000000007</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C71" s="21">
+        <f t="shared" si="7"/>
+        <v>39819.199999999997</v>
+      </c>
+      <c r="D71" s="21">
+        <f t="shared" si="8"/>
+        <v>1984.1999999999971</v>
+      </c>
+      <c r="E71" s="21">
+        <f>MAX($D$56:D71)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5">
         <v>16</v>
       </c>
       <c r="B72" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>878.31666666666672</v>
       </c>
-      <c r="C72" s="17">
-        <f t="shared" si="11"/>
-        <v>44577.1</v>
-      </c>
-      <c r="D72" s="17">
-        <f t="shared" si="13"/>
-        <v>3138.6999999999971</v>
-      </c>
-      <c r="E72" s="17">
-        <f t="shared" si="12"/>
-        <v>29328.6</v>
-      </c>
-      <c r="F72" s="17">
-        <f t="shared" si="14"/>
-        <v>2009.3999999999978</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C72" s="21">
+        <f t="shared" si="7"/>
+        <v>41828.6</v>
+      </c>
+      <c r="D72" s="21">
+        <f t="shared" si="8"/>
+        <v>2009.4000000000015</v>
+      </c>
+      <c r="E72" s="21">
+        <f>MAX($D$56:D72)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5">
         <v>17</v>
       </c>
       <c r="B73" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>944.88333333333333</v>
       </c>
-      <c r="C73" s="17">
-        <f t="shared" si="11"/>
-        <v>47768.4</v>
-      </c>
-      <c r="D73" s="17">
-        <f t="shared" si="13"/>
-        <v>3191.3000000000029</v>
-      </c>
-      <c r="E73" s="17">
-        <f t="shared" si="12"/>
-        <v>31364.2</v>
-      </c>
-      <c r="F73" s="17">
-        <f t="shared" si="14"/>
-        <v>2035.6000000000022</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C73" s="21">
+        <f t="shared" si="7"/>
+        <v>43864.2</v>
+      </c>
+      <c r="D73" s="21">
+        <f t="shared" si="8"/>
+        <v>2035.5999999999985</v>
+      </c>
+      <c r="E73" s="21">
+        <f>MAX($D$56:D73)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5">
         <v>18</v>
       </c>
       <c r="B74" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1012.9666666666667</v>
       </c>
-      <c r="C74" s="17">
-        <f t="shared" si="11"/>
-        <v>51012.5</v>
-      </c>
-      <c r="D74" s="17">
-        <f t="shared" si="13"/>
-        <v>3244.0999999999985</v>
-      </c>
-      <c r="E74" s="17">
-        <f t="shared" si="12"/>
-        <v>33426.199999999997</v>
-      </c>
-      <c r="F74" s="17">
-        <f t="shared" si="14"/>
-        <v>2061.9999999999964</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C74" s="21">
+        <f t="shared" si="7"/>
+        <v>45926.2</v>
+      </c>
+      <c r="D74" s="21">
+        <f t="shared" si="8"/>
+        <v>2062</v>
+      </c>
+      <c r="E74" s="21">
+        <f>MAX($D$56:D74)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5">
         <v>19</v>
       </c>
       <c r="B75" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1082.6166666666666</v>
       </c>
-      <c r="C75" s="17">
-        <f t="shared" si="11"/>
-        <v>54310.9</v>
-      </c>
-      <c r="D75" s="17">
-        <f t="shared" si="13"/>
-        <v>3298.4000000000015</v>
-      </c>
-      <c r="E75" s="17">
-        <f t="shared" si="12"/>
-        <v>35515.4</v>
-      </c>
-      <c r="F75" s="17">
-        <f t="shared" si="14"/>
+      <c r="C75" s="21">
+        <f t="shared" si="7"/>
+        <v>48015.4</v>
+      </c>
+      <c r="D75" s="21">
+        <f t="shared" si="8"/>
         <v>2089.2000000000044</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E75" s="21">
+        <f>MAX($D$56:D75)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5">
         <v>20</v>
       </c>
       <c r="B76" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1153.8333333333333</v>
       </c>
-      <c r="C76" s="17">
-        <f t="shared" si="11"/>
-        <v>57663.7</v>
-      </c>
-      <c r="D76" s="17">
-        <f t="shared" si="13"/>
-        <v>3352.7999999999956</v>
-      </c>
-      <c r="E76" s="17">
-        <f t="shared" si="12"/>
-        <v>37631.800000000003</v>
-      </c>
-      <c r="F76" s="17">
-        <f t="shared" si="14"/>
+      <c r="C76" s="21">
+        <f t="shared" si="7"/>
+        <v>50131.8</v>
+      </c>
+      <c r="D76" s="21">
+        <f t="shared" si="8"/>
         <v>2116.4000000000015</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E76" s="21">
+        <f>MAX($D$56:D76)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5">
         <v>21</v>
       </c>
       <c r="B77" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1226.6666666666667</v>
       </c>
-      <c r="C77" s="17">
-        <f t="shared" si="11"/>
-        <v>61072.6</v>
-      </c>
-      <c r="D77" s="17">
-        <f t="shared" si="13"/>
-        <v>3408.9000000000015</v>
-      </c>
-      <c r="E77" s="17">
-        <f t="shared" si="12"/>
-        <v>39776.300000000003</v>
-      </c>
-      <c r="F77" s="17">
-        <f t="shared" si="14"/>
+      <c r="C77" s="21">
+        <f t="shared" si="7"/>
+        <v>52276.3</v>
+      </c>
+      <c r="D77" s="21">
+        <f t="shared" si="8"/>
         <v>2144.5</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E77" s="21">
+        <f>MAX($D$56:D77)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5">
         <v>22</v>
       </c>
       <c r="B78" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1301.1500000000001</v>
       </c>
-      <c r="C78" s="17">
-        <f t="shared" si="11"/>
-        <v>64538.8</v>
-      </c>
-      <c r="D78" s="17">
-        <f t="shared" si="13"/>
-        <v>3466.2000000000044</v>
-      </c>
-      <c r="E78" s="17">
-        <f t="shared" si="12"/>
-        <v>41949.4</v>
-      </c>
-      <c r="F78" s="17">
-        <f t="shared" si="14"/>
+      <c r="C78" s="21">
+        <f t="shared" si="7"/>
+        <v>54449.4</v>
+      </c>
+      <c r="D78" s="21">
+        <f t="shared" si="8"/>
         <v>2173.0999999999985</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E78" s="21">
+        <f>MAX($D$56:D78)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5">
         <v>23</v>
       </c>
       <c r="B79" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1377.3</v>
       </c>
-      <c r="C79" s="17">
-        <f t="shared" si="11"/>
-        <v>68062.899999999994</v>
-      </c>
-      <c r="D79" s="17">
-        <f t="shared" si="13"/>
-        <v>3524.0999999999913</v>
-      </c>
-      <c r="E79" s="17">
-        <f t="shared" si="12"/>
-        <v>44151.5</v>
-      </c>
-      <c r="F79" s="17">
-        <f t="shared" si="14"/>
+      <c r="C79" s="21">
+        <f t="shared" si="7"/>
+        <v>56651.5</v>
+      </c>
+      <c r="D79" s="21">
+        <f t="shared" si="8"/>
         <v>2202.0999999999985</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E79" s="21">
+        <f>MAX($D$56:D79)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5">
         <v>24</v>
       </c>
       <c r="B80" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1455.1333333333334</v>
       </c>
-      <c r="C80" s="17">
-        <f t="shared" si="11"/>
-        <v>71645.5</v>
-      </c>
-      <c r="D80" s="17">
-        <f t="shared" si="13"/>
-        <v>3582.6000000000058</v>
-      </c>
-      <c r="E80" s="17">
-        <f t="shared" si="12"/>
-        <v>46382.7</v>
-      </c>
-      <c r="F80" s="17">
-        <f t="shared" si="14"/>
+      <c r="C80" s="21">
+        <f t="shared" si="7"/>
+        <v>58882.7</v>
+      </c>
+      <c r="D80" s="21">
+        <f t="shared" si="8"/>
         <v>2231.1999999999971</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E80" s="21">
+        <f>MAX($D$56:D80)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5">
         <v>25</v>
       </c>
       <c r="B81" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1534.7166666666667</v>
       </c>
-      <c r="C81" s="17">
-        <f t="shared" si="11"/>
-        <v>75288.800000000003</v>
-      </c>
-      <c r="D81" s="17">
-        <f t="shared" si="13"/>
-        <v>3643.3000000000029</v>
-      </c>
-      <c r="E81" s="17">
-        <f t="shared" si="12"/>
-        <v>48644.4</v>
-      </c>
-      <c r="F81" s="17">
-        <f t="shared" si="14"/>
+      <c r="C81" s="21">
+        <f t="shared" si="7"/>
+        <v>61144.4</v>
+      </c>
+      <c r="D81" s="21">
+        <f t="shared" si="8"/>
         <v>2261.7000000000044</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E81" s="21">
+        <f>MAX($D$56:D81)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="5">
         <v>26</v>
       </c>
       <c r="B82" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1616.05</v>
       </c>
-      <c r="C82" s="17">
-        <f t="shared" si="11"/>
-        <v>78992.800000000003</v>
-      </c>
-      <c r="D82" s="17">
-        <f t="shared" si="13"/>
-        <v>3704</v>
-      </c>
-      <c r="E82" s="17">
-        <f t="shared" si="12"/>
-        <v>50936.4</v>
-      </c>
-      <c r="F82" s="17">
-        <f t="shared" si="14"/>
+      <c r="C82" s="21">
+        <f t="shared" si="7"/>
+        <v>63436.4</v>
+      </c>
+      <c r="D82" s="21">
+        <f t="shared" si="8"/>
         <v>2292</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E82" s="21">
+        <f>MAX($D$56:D82)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5">
         <v>27</v>
       </c>
       <c r="B83" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1699.1833333333334</v>
       </c>
-      <c r="C83" s="17">
-        <f t="shared" si="11"/>
-        <v>82759.399999999994</v>
-      </c>
-      <c r="D83" s="17">
-        <f t="shared" si="13"/>
-        <v>3766.5999999999913</v>
-      </c>
-      <c r="E83" s="17">
-        <f t="shared" si="12"/>
-        <v>53259.7</v>
-      </c>
-      <c r="F83" s="17">
-        <f t="shared" si="14"/>
+      <c r="C83" s="21">
+        <f t="shared" si="7"/>
+        <v>65759.7</v>
+      </c>
+      <c r="D83" s="21">
+        <f t="shared" si="8"/>
         <v>2323.2999999999956</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E83" s="21">
+        <f>MAX($D$56:D83)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5">
         <v>28</v>
       </c>
       <c r="B84" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1784.15</v>
       </c>
-      <c r="C84" s="17">
-        <f t="shared" si="11"/>
-        <v>86589.7</v>
-      </c>
-      <c r="D84" s="17">
-        <f t="shared" si="13"/>
-        <v>3830.3000000000029</v>
-      </c>
-      <c r="E84" s="17">
-        <f t="shared" si="12"/>
-        <v>55614.8</v>
-      </c>
-      <c r="F84" s="17">
-        <f t="shared" si="14"/>
+      <c r="C84" s="21">
+        <f t="shared" si="7"/>
+        <v>68114.8</v>
+      </c>
+      <c r="D84" s="21">
+        <f t="shared" si="8"/>
         <v>2355.1000000000058</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E84" s="21">
+        <f>MAX($D$56:D84)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5">
         <v>29</v>
       </c>
       <c r="B85" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1870.9666666666667</v>
       </c>
-      <c r="C85" s="17">
-        <f t="shared" si="11"/>
-        <v>90484.1</v>
-      </c>
-      <c r="D85" s="17">
-        <f t="shared" si="13"/>
-        <v>3894.4000000000087</v>
-      </c>
-      <c r="E85" s="17">
-        <f t="shared" si="12"/>
-        <v>58002.1</v>
-      </c>
-      <c r="F85" s="17">
-        <f t="shared" si="14"/>
-        <v>2387.2999999999956</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="C85" s="21">
+        <f t="shared" si="7"/>
+        <v>70502.100000000006</v>
+      </c>
+      <c r="D85" s="21">
+        <f t="shared" si="8"/>
+        <v>2387.3000000000029</v>
+      </c>
+      <c r="E85" s="21">
+        <f>MAX($D$56:D85)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5">
         <v>30</v>
       </c>
       <c r="B86" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>1959.6833333333334</v>
       </c>
-      <c r="C86" s="17">
-        <f t="shared" si="11"/>
-        <v>94444.6</v>
-      </c>
-      <c r="D86" s="17">
-        <f t="shared" si="13"/>
-        <v>3960.5</v>
-      </c>
-      <c r="E86" s="17">
-        <f t="shared" si="12"/>
-        <v>60422.3</v>
-      </c>
-      <c r="F86" s="17">
-        <f t="shared" si="14"/>
-        <v>2420.2000000000044</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D87" s="25">
-        <f>SUMPRODUCT(MAX((D56:D86&lt;=MES_PRICE)*A56:A86))</f>
+      <c r="C86" s="21">
+        <f t="shared" si="7"/>
+        <v>72922.3</v>
+      </c>
+      <c r="D86" s="21">
+        <f t="shared" si="8"/>
+        <v>2420.1999999999971</v>
+      </c>
+      <c r="E86" s="21">
+        <f>MAX($D$56:D86)</f>
+        <v>2988.7999999999956</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D87" s="28">
+        <f>SUMPRODUCT((E56:E86&lt;=MES_PRICE)*1)-1</f>
         <v>6</v>
       </c>
-      <c r="F87" s="25">
-        <f>SUMPRODUCT(MAX((F56:F86&lt;=MES_PRICE)*A56:A86))</f>
-        <v>30</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A27"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A87"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A54:G54"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A52"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A54:G54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4261,7 +4136,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4269,8 +4144,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="24" t="s">
-        <v>144</v>
+      <c r="A1" s="27" t="s">
+        <v>157</v>
       </c>
       <c r="B1" s="13"/>
     </row>
@@ -4279,27 +4154,27 @@
       <c r="B2" s="13"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="24" t="s">
-        <v>145</v>
+      <c r="A3" s="27" t="s">
+        <v>158</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="13" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="24" t="s">
-        <v>149</v>
+      <c r="A5" s="27" t="s">
+        <v>162</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4307,65 +4182,65 @@
       <c r="B6" s="13"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="24" t="s">
-        <v>151</v>
+      <c r="A7" s="27" t="s">
+        <v>164</v>
       </c>
       <c r="B7" s="13"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="13" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="13" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="13" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="13" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="13" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="13" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4374,10 +4249,10 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="13" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4386,13 +4261,13 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B18" s="13"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="13" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B19" s="13">
         <v>10</v>
@@ -4400,7 +4275,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="13" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B20" s="13">
         <v>20</v>
@@ -4408,7 +4283,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="13" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B21" s="13">
         <v>30</v>
@@ -4416,10 +4291,46 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="13" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>170</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richi\AppData\Local\Temp\claude\C--Users-richi-OneDrive-Desktop-DLEMBA--BUS-620--Micro--and-Macro-Economic-Foundations-for-Managers\cfc02a1c-a830-4c87-8d1b-4489c63015ae\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8782DC-7115-4D17-B138-6F8F28D8BF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13A783B-652E-4359-B2B4-EC86DB8B1CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="192">
   <si>
     <t>Marginal analysis - perfect competition (post-review build 2026-09-24)</t>
   </si>
@@ -671,6 +671,12 @@
   </si>
   <si>
     <t>proof of global optimality; this corroborates it. See spec.md for detail.</t>
+  </si>
+  <si>
+    <t>JOINT-CONTEXT CARROT MC (TOM and MES held at the current decision-cell levels: 10 / 30)</t>
+  </si>
+  <si>
+    <t>TOTAL_HRS(q)</t>
   </si>
 </sst>
 </file>
@@ -686,7 +692,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0000&quot; hrs&quot;"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +735,22 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -786,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -822,10 +844,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,6 +865,1511 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Tomatoes: marginal cost vs price (farmer-first tiered, standalone)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Marginal cost</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$A$6:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$D$6:$D$26</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4317.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5795.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6703.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7660.7000000000007</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4906.2999999999993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5585.6999999999971</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6360.6000000000058</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7243.7999999999956</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8248.5999999999985</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9390.6999999999971</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10687.600000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12158.600000000006</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>13826.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15713.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17850.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20264.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22993.400000000023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26073.299999999988</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>29548.399999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A819-4783-816F-90AB57B4092E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Price</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$A$6:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$G$6:$G$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A819-4783-816F-90AB57B4092E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="477099999"/>
+        <c:axId val="362342799"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="477099999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Beds planted (q)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="362342799"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="362342799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="\$#,##0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="477099999"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Carrots: marginal cost vs price (farmer-first tiered, standalone)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Marginal cost</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$A$31:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$D$31:$D$51</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1507.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1560.9999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1616.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1673.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1733.8999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1795.3999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1858.9000000000015</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1926.1999999999989</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1994.8999999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2066.2000000000007</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2139.5999999999985</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2217.2000000000007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2295.9000000000015</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2378.7000000000007</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2463.6999999999971</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2552.3000000000029</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1670.9000000000015</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1589</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1638.1999999999971</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1688.9000000000015</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2CC3-4EEC-AF3A-8FD29B083F1D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Price</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$A$31:$A$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$G$31:$G$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2CC3-4EEC-AF3A-8FD29B083F1D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="491937103"/>
+        <c:axId val="362315919"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="491937103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Beds planted (q)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="362315919"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="362315919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="\$#,##0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="491937103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Carrots: joint-context marginal cost vs price (TOM=10, MES=30 held fixed)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Marginal cost</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$A$92:$A$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$D$92:$D$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>973.79999999998836</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1028.3000000000175</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1056.8999999999942</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1086.8999999999942</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1117.7000000000116</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1149.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1183.1000000000058</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1217.3999999999942</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1253.1000000000058</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1289.8999999999942</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1328.6000000000058</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1367.8999999999942</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1409.2999999999884</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1451.8999999999942</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1496.1000000000058</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1541.8999999999942</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1589</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1638.2000000000116</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1688.7999999999884</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-007F-48C5-8B76-DEC0EA68103E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Price</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$A$92:$A$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Standalone Diagnostics'!$G$92:$G$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-007F-48C5-8B76-DEC0EA68103E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="865797184"/>
+        <c:axId val="1316484528"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="865797184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Beds planted (q)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1316484528"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1316484528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="865797184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>134620</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2755900</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>54610</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5854FD90-1076-A461-10C7-D6C4AB1614A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>134620</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>181610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2755900</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>151130</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAED5B15-6FAB-B46A-9DB7-7E6F0A23989D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>134620</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>39370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2755900</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>8890</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F11E18B-D620-8CDF-9F07-2588B6836179}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1138,37 +2667,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
@@ -1292,15 +2821,15 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
@@ -1459,15 +2988,15 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
@@ -1522,15 +3051,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
@@ -1577,15 +3106,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
@@ -1666,15 +3195,15 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
@@ -1781,15 +3310,15 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
@@ -1890,15 +3419,15 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
@@ -2032,15 +3561,15 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
@@ -2150,257 +3679,257 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="30"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="32"/>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
+      <c r="B85" s="32"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="29" t="s">
+      <c r="A87" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="B88" s="30"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="B89" s="30"/>
-      <c r="C89" s="30"/>
-      <c r="D89" s="30"/>
-      <c r="E89" s="30"/>
-      <c r="F89" s="30"/>
-      <c r="G89" s="30"/>
+      <c r="B89" s="32"/>
+      <c r="C89" s="32"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="32"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="32"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="29" t="s">
+      <c r="A90" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="30"/>
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="30"/>
-      <c r="G90" s="30"/>
+      <c r="B90" s="32"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="32"/>
+      <c r="F90" s="32"/>
+      <c r="G90" s="32"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="29" t="s">
+      <c r="A91" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="32"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="32"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="29" t="s">
+      <c r="A92" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="B92" s="30"/>
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="32"/>
+      <c r="F92" s="32"/>
+      <c r="G92" s="32"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="29" t="s">
+      <c r="A93" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="30"/>
-      <c r="C93" s="30"/>
-      <c r="D93" s="30"/>
-      <c r="E93" s="30"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+      <c r="G93" s="32"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="29" t="s">
+      <c r="A94" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="B94" s="30"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="30"/>
+      <c r="B94" s="32"/>
+      <c r="C94" s="32"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="32"/>
+      <c r="F94" s="32"/>
+      <c r="G94" s="32"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="29" t="s">
+      <c r="A95" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="B95" s="30"/>
-      <c r="C95" s="30"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="30"/>
-      <c r="G95" s="30"/>
+      <c r="B95" s="32"/>
+      <c r="C95" s="32"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="32"/>
+      <c r="F95" s="32"/>
+      <c r="G95" s="32"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="29" t="s">
+      <c r="A96" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
+      <c r="B96" s="32"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="32"/>
+      <c r="F96" s="32"/>
+      <c r="G96" s="32"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="29" t="s">
+      <c r="A97" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="B97" s="30"/>
-      <c r="C97" s="30"/>
-      <c r="D97" s="30"/>
-      <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
+      <c r="B97" s="32"/>
+      <c r="C97" s="32"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="32"/>
+      <c r="F97" s="32"/>
+      <c r="G97" s="32"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="30"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
-      <c r="F98" s="30"/>
-      <c r="G98" s="30"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="32"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="29" t="s">
+      <c r="A99" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="29" t="s">
+      <c r="A100" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="29" t="s">
+      <c r="A101" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="30"/>
-      <c r="C101" s="30"/>
-      <c r="D101" s="30"/>
-      <c r="E101" s="30"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="29" t="s">
+      <c r="A102" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="30"/>
-      <c r="C102" s="30"/>
-      <c r="D102" s="30"/>
-      <c r="E102" s="30"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30"/>
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
+      <c r="E102" s="32"/>
+      <c r="F102" s="32"/>
+      <c r="G102" s="32"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="29" t="s">
+      <c r="A103" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
+      <c r="B103" s="32"/>
+      <c r="C103" s="32"/>
+      <c r="D103" s="32"/>
+      <c r="E103" s="32"/>
+      <c r="F103" s="32"/>
+      <c r="G103" s="32"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="29" t="s">
+      <c r="A104" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="30"/>
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="30"/>
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="32"/>
+      <c r="F104" s="32"/>
+      <c r="G104" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -2410,6 +3939,18 @@
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="A103:G103"/>
+    <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A102:G102"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A98:G98"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A91:G91"/>
+    <mergeCell ref="A96:G96"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A88:G88"/>
     <mergeCell ref="A70:G70"/>
@@ -2418,26 +3959,14 @@
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A90:G90"/>
-    <mergeCell ref="A99:G99"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A89:G89"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A101:G101"/>
-    <mergeCell ref="A102:G102"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A98:G98"/>
-    <mergeCell ref="A97:G97"/>
-    <mergeCell ref="A91:G91"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A100:G100"/>
-    <mergeCell ref="A96:G96"/>
-    <mergeCell ref="A93:G93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2445,7 +3974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2454,37 +3983,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
@@ -2503,7 +4032,9 @@
         <v>153</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
@@ -2524,6 +4055,10 @@
         <f>MAX($D$6:D6)</f>
         <v>0</v>
       </c>
+      <c r="G6" s="29">
+        <f t="shared" ref="G6:G26" si="2">TOM_PRICE</f>
+        <v>8800</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5">
@@ -2538,13 +4073,17 @@
         <v>4317.5</v>
       </c>
       <c r="D7" s="21">
-        <f t="shared" ref="D7:D26" si="2">C7-C6</f>
+        <f t="shared" ref="D7:D26" si="3">C7-C6</f>
         <v>4317.5</v>
       </c>
       <c r="E7" s="21">
         <f>MAX($D$6:D7)</f>
         <v>4317.5</v>
       </c>
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
@@ -2559,13 +4098,17 @@
         <v>9322.5</v>
       </c>
       <c r="D8" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5005</v>
       </c>
       <c r="E8" s="21">
         <f>MAX($D$6:D8)</f>
         <v>5005</v>
       </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
@@ -2580,13 +4123,17 @@
         <v>15118</v>
       </c>
       <c r="D9" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5795.5</v>
       </c>
       <c r="E9" s="21">
         <f>MAX($D$6:D9)</f>
         <v>5795.5</v>
       </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5">
@@ -2601,13 +4148,17 @@
         <v>21821.5</v>
       </c>
       <c r="D10" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6703.5</v>
       </c>
       <c r="E10" s="21">
         <f>MAX($D$6:D10)</f>
         <v>6703.5</v>
       </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5">
@@ -2622,13 +4173,17 @@
         <v>29482.2</v>
       </c>
       <c r="D11" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7660.7000000000007</v>
       </c>
       <c r="E11" s="21">
         <f>MAX($D$6:D11)</f>
         <v>7660.7000000000007</v>
       </c>
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5">
@@ -2643,13 +4198,17 @@
         <v>34388.5</v>
       </c>
       <c r="D12" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4906.2999999999993</v>
       </c>
       <c r="E12" s="21">
         <f>MAX($D$6:D12)</f>
         <v>7660.7000000000007</v>
       </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5">
@@ -2664,13 +4223,17 @@
         <v>39974.199999999997</v>
       </c>
       <c r="D13" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5585.6999999999971</v>
       </c>
       <c r="E13" s="21">
         <f>MAX($D$6:D13)</f>
         <v>7660.7000000000007</v>
       </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5">
@@ -2685,13 +4248,17 @@
         <v>46334.8</v>
       </c>
       <c r="D14" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6360.6000000000058</v>
       </c>
       <c r="E14" s="21">
         <f>MAX($D$6:D14)</f>
         <v>7660.7000000000007</v>
       </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5">
@@ -2706,13 +4273,17 @@
         <v>53578.6</v>
       </c>
       <c r="D15" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7243.7999999999956</v>
       </c>
       <c r="E15" s="21">
         <f>MAX($D$6:D15)</f>
         <v>7660.7000000000007</v>
       </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5">
@@ -2727,13 +4298,17 @@
         <v>61827.199999999997</v>
       </c>
       <c r="D16" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8248.5999999999985</v>
       </c>
       <c r="E16" s="21">
         <f>MAX($D$6:D16)</f>
         <v>8248.5999999999985</v>
       </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5">
@@ -2748,13 +4323,17 @@
         <v>71217.899999999994</v>
       </c>
       <c r="D17" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9390.6999999999971</v>
       </c>
       <c r="E17" s="21">
         <f>MAX($D$6:D17)</f>
         <v>9390.6999999999971</v>
       </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5">
@@ -2769,13 +4348,17 @@
         <v>81905.5</v>
       </c>
       <c r="D18" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10687.600000000006</v>
       </c>
       <c r="E18" s="21">
         <f>MAX($D$6:D18)</f>
         <v>10687.600000000006</v>
       </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5">
@@ -2790,13 +4373,17 @@
         <v>94064.1</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12158.600000000006</v>
       </c>
       <c r="E19" s="21">
         <f>MAX($D$6:D19)</f>
         <v>12158.600000000006</v>
       </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5">
@@ -2811,13 +4398,17 @@
         <v>107890.3</v>
       </c>
       <c r="D20" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13826.199999999997</v>
       </c>
       <c r="E20" s="21">
         <f>MAX($D$6:D20)</f>
         <v>13826.199999999997</v>
       </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5">
@@ -2832,13 +4423,17 @@
         <v>123604.2</v>
       </c>
       <c r="D21" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15713.899999999994</v>
       </c>
       <c r="E21" s="21">
         <f>MAX($D$6:D21)</f>
         <v>15713.899999999994</v>
       </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5">
@@ -2853,13 +4448,17 @@
         <v>141454.39999999999</v>
       </c>
       <c r="D22" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17850.199999999997</v>
       </c>
       <c r="E22" s="21">
         <f>MAX($D$6:D22)</f>
         <v>17850.199999999997</v>
       </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5">
@@ -2874,13 +4473,17 @@
         <v>161719.29999999999</v>
       </c>
       <c r="D23" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20264.899999999994</v>
       </c>
       <c r="E23" s="21">
         <f>MAX($D$6:D23)</f>
         <v>20264.899999999994</v>
       </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5">
@@ -2895,13 +4498,17 @@
         <v>184712.7</v>
       </c>
       <c r="D24" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22993.400000000023</v>
       </c>
       <c r="E24" s="21">
         <f>MAX($D$6:D24)</f>
         <v>22993.400000000023</v>
       </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5">
@@ -2916,13 +4523,17 @@
         <v>210786</v>
       </c>
       <c r="D25" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26073.299999999988</v>
       </c>
       <c r="E25" s="21">
         <f>MAX($D$6:D25)</f>
         <v>26073.299999999988</v>
       </c>
+      <c r="G25">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5">
@@ -2937,13 +4548,17 @@
         <v>240334.4</v>
       </c>
       <c r="D26" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>29548.399999999994</v>
       </c>
       <c r="E26" s="21">
         <f>MAX($D$6:D26)</f>
         <v>29548.399999999994</v>
       </c>
+      <c r="G26">
+        <f t="shared" si="2"/>
+        <v>8800</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="27" t="s">
@@ -2955,15 +4570,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
@@ -2982,18 +4597,20 @@
         <v>153</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="5">
         <v>0</v>
       </c>
       <c r="B31" s="15">
-        <f t="shared" ref="B31:B51" si="3">ROUND(A31*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A31*60,0)/60</f>
+        <f t="shared" ref="B31:B51" si="4">ROUND(A31*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A31*60,0)/60</f>
         <v>0</v>
       </c>
       <c r="C31" s="21">
-        <f t="shared" ref="C31:C51" si="4">ROUND(IF(B31&lt;=FARMER_HRS_CAP,B31*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B31-FARMER_HRS_CAP)*TEMP_RATE)+A31*CAR_FERT_COST,1)</f>
+        <f t="shared" ref="C31:C51" si="5">ROUND(IF(B31&lt;=FARMER_HRS_CAP,B31*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B31-FARMER_HRS_CAP)*TEMP_RATE)+A31*CAR_FERT_COST,1)</f>
         <v>0</v>
       </c>
       <c r="D31" s="21">
@@ -3003,426 +4620,510 @@
         <f>MAX($D$31:D31)</f>
         <v>0</v>
       </c>
+      <c r="G31">
+        <f t="shared" ref="G31:G51" si="6">CAR_PRICE</f>
+        <v>2094</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5">
         <v>1</v>
       </c>
       <c r="B32" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>30.75</v>
       </c>
       <c r="C32" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1507.7</v>
       </c>
       <c r="D32" s="21">
-        <f t="shared" ref="D32:D51" si="5">C32-C31</f>
+        <f t="shared" ref="D32:D51" si="7">C32-C31</f>
         <v>1507.7</v>
       </c>
       <c r="E32" s="21">
         <f>MAX($D$31:D32)</f>
         <v>1507.7</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G32">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5">
         <v>2</v>
       </c>
       <c r="B33" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>63.033333333333331</v>
       </c>
       <c r="C33" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3068.7</v>
       </c>
       <c r="D33" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1560.9999999999998</v>
       </c>
       <c r="E33" s="21">
         <f>MAX($D$31:D33)</f>
         <v>1560.9999999999998</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G33">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5">
         <v>3</v>
       </c>
       <c r="B34" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>96.916666666666671</v>
       </c>
       <c r="C34" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4685.2</v>
       </c>
       <c r="D34" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1616.5</v>
       </c>
       <c r="E34" s="21">
         <f>MAX($D$31:D34)</f>
         <v>1616.5</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G34">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5">
         <v>4</v>
       </c>
       <c r="B35" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>132.44999999999999</v>
       </c>
       <c r="C35" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6359</v>
       </c>
       <c r="D35" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1673.8000000000002</v>
       </c>
       <c r="E35" s="21">
         <f>MAX($D$31:D35)</f>
         <v>1673.8000000000002</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G35">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5">
         <v>5</v>
       </c>
       <c r="B36" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>169.71666666666667</v>
       </c>
       <c r="C36" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8092.9</v>
       </c>
       <c r="D36" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1733.8999999999996</v>
       </c>
       <c r="E36" s="21">
         <f>MAX($D$31:D36)</f>
         <v>1733.8999999999996</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G36">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5">
         <v>6</v>
       </c>
       <c r="B37" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>208.75</v>
       </c>
       <c r="C37" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9888.2999999999993</v>
       </c>
       <c r="D37" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1795.3999999999996</v>
       </c>
       <c r="E37" s="21">
         <f>MAX($D$31:D37)</f>
         <v>1795.3999999999996</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G37">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="5">
         <v>7</v>
       </c>
       <c r="B38" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>249.61666666666667</v>
       </c>
       <c r="C38" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11747.2</v>
       </c>
       <c r="D38" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1858.9000000000015</v>
       </c>
       <c r="E38" s="21">
         <f>MAX($D$31:D38)</f>
         <v>1858.9000000000015</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G38">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5">
         <v>8</v>
       </c>
       <c r="B39" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>292.41666666666669</v>
       </c>
       <c r="C39" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13673.4</v>
       </c>
       <c r="D39" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1926.1999999999989</v>
       </c>
       <c r="E39" s="21">
         <f>MAX($D$31:D39)</f>
         <v>1926.1999999999989</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G39">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5">
         <v>9</v>
       </c>
       <c r="B40" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>337.2</v>
       </c>
       <c r="C40" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15668.3</v>
       </c>
       <c r="D40" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1994.8999999999996</v>
       </c>
       <c r="E40" s="21">
         <f>MAX($D$31:D40)</f>
         <v>1994.8999999999996</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G40">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5">
         <v>10</v>
       </c>
       <c r="B41" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>384.03333333333336</v>
       </c>
       <c r="C41" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17734.5</v>
       </c>
       <c r="D41" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2066.2000000000007</v>
       </c>
       <c r="E41" s="21">
         <f>MAX($D$31:D41)</f>
         <v>2066.2000000000007</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G41">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5">
         <v>11</v>
       </c>
       <c r="B42" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>432.98333333333335</v>
       </c>
       <c r="C42" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19874.099999999999</v>
       </c>
       <c r="D42" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2139.5999999999985</v>
       </c>
       <c r="E42" s="21">
         <f>MAX($D$31:D42)</f>
         <v>2139.5999999999985</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G42">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5">
         <v>12</v>
       </c>
       <c r="B43" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>484.16666666666669</v>
       </c>
       <c r="C43" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22091.3</v>
       </c>
       <c r="D43" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2217.2000000000007</v>
       </c>
       <c r="E43" s="21">
         <f>MAX($D$31:D43)</f>
         <v>2217.2000000000007</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G43">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5">
         <v>13</v>
       </c>
       <c r="B44" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>537.61666666666667</v>
       </c>
       <c r="C44" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>24387.200000000001</v>
       </c>
       <c r="D44" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2295.9000000000015</v>
       </c>
       <c r="E44" s="21">
         <f>MAX($D$31:D44)</f>
         <v>2295.9000000000015</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G44">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5">
         <v>14</v>
       </c>
       <c r="B45" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>593.45000000000005</v>
       </c>
       <c r="C45" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26765.9</v>
       </c>
       <c r="D45" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2378.7000000000007</v>
       </c>
       <c r="E45" s="21">
         <f>MAX($D$31:D45)</f>
         <v>2378.7000000000007</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G45">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5">
         <v>15</v>
       </c>
       <c r="B46" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>651.73333333333335</v>
       </c>
       <c r="C46" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29229.599999999999</v>
       </c>
       <c r="D46" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2463.6999999999971</v>
       </c>
       <c r="E46" s="21">
         <f>MAX($D$31:D46)</f>
         <v>2463.6999999999971</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G46">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="5">
         <v>16</v>
       </c>
       <c r="B47" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>712.56666666666672</v>
       </c>
       <c r="C47" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>31781.9</v>
       </c>
       <c r="D47" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2552.3000000000029</v>
       </c>
       <c r="E47" s="21">
         <f>MAX($D$31:D47)</f>
         <v>2552.3000000000029</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G47">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5">
         <v>17</v>
       </c>
       <c r="B48" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>776.0333333333333</v>
       </c>
       <c r="C48" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33452.800000000003</v>
       </c>
       <c r="D48" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1670.9000000000015</v>
       </c>
       <c r="E48" s="21">
         <f>MAX($D$31:D48)</f>
         <v>2552.3000000000029</v>
       </c>
+      <c r="G48">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="5">
         <v>18</v>
       </c>
       <c r="B49" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>842.2166666666667</v>
       </c>
       <c r="C49" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>35041.800000000003</v>
       </c>
       <c r="D49" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1589</v>
       </c>
       <c r="E49" s="21">
         <f>MAX($D$31:D49)</f>
         <v>2552.3000000000029</v>
       </c>
+      <c r="G49">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="5">
         <v>19</v>
       </c>
       <c r="B50" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>911.23333333333335</v>
       </c>
       <c r="C50" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>36680</v>
       </c>
       <c r="D50" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1638.1999999999971</v>
       </c>
       <c r="E50" s="21">
         <f>MAX($D$31:D50)</f>
         <v>2552.3000000000029</v>
       </c>
+      <c r="G50">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="5">
         <v>20</v>
       </c>
       <c r="B51" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>983.16666666666663</v>
       </c>
       <c r="C51" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>38368.9</v>
       </c>
       <c r="D51" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1688.9000000000015</v>
       </c>
       <c r="E51" s="21">
         <f>MAX($D$31:D51)</f>
         <v>2552.3000000000029</v>
       </c>
+      <c r="G51">
+        <f t="shared" si="6"/>
+        <v>2094</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="27" t="s">
@@ -3434,15 +5135,15 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
@@ -3461,18 +5162,20 @@
         <v>153</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="5">
         <v>0</v>
       </c>
       <c r="B56" s="15">
-        <f t="shared" ref="B56:B86" si="6">ROUND(A56*MES_HRS*WEEKS*(1+MES_DIM_PCT)^A56*60,0)/60</f>
+        <f t="shared" ref="B56:B86" si="8">ROUND(A56*MES_HRS*WEEKS*(1+MES_DIM_PCT)^A56*60,0)/60</f>
         <v>0</v>
       </c>
       <c r="C56" s="21">
-        <f t="shared" ref="C56:C86" si="7">ROUND(IF(B56&lt;=FARMER_HRS_CAP,B56*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B56-FARMER_HRS_CAP)*TEMP_RATE)+A56*MES_FERT_COST,1)</f>
+        <f t="shared" ref="C56:C86" si="9">ROUND(IF(B56&lt;=FARMER_HRS_CAP,B56*FARMER_RATE,FARMER_HRS_CAP*FARMER_RATE+(B56-FARMER_HRS_CAP)*TEMP_RATE)+A56*MES_FERT_COST,1)</f>
         <v>0</v>
       </c>
       <c r="D56" s="21">
@@ -3482,644 +5185,1227 @@
         <f>MAX($D$56:D56)</f>
         <v>0</v>
       </c>
+      <c r="G56">
+        <f t="shared" ref="G56:G86" si="10">MES_PRICE</f>
+        <v>2700</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="5">
         <v>1</v>
       </c>
       <c r="B57" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>45.56666666666667</v>
       </c>
       <c r="C57" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2462.1999999999998</v>
       </c>
       <c r="D57" s="21">
-        <f t="shared" ref="D57:D86" si="8">C57-C56</f>
+        <f t="shared" ref="D57:D86" si="11">C57-C56</f>
         <v>2462.1999999999998</v>
       </c>
       <c r="E57" s="21">
         <f>MAX($D$56:D57)</f>
         <v>2462.1999999999998</v>
       </c>
+      <c r="G57">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="5">
         <v>2</v>
       </c>
       <c r="B58" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>92.266666666666666</v>
       </c>
       <c r="C58" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4963.7</v>
       </c>
       <c r="D58" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2501.5</v>
       </c>
       <c r="E58" s="21">
         <f>MAX($D$56:D58)</f>
         <v>2501.5</v>
       </c>
+      <c r="G58">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="5">
         <v>3</v>
       </c>
       <c r="B59" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>140.13333333333333</v>
       </c>
       <c r="C59" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7505.7</v>
       </c>
       <c r="D59" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2542</v>
       </c>
       <c r="E59" s="21">
         <f>MAX($D$56:D59)</f>
         <v>2542</v>
       </c>
+      <c r="G59">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="5">
         <v>4</v>
       </c>
       <c r="B60" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>189.16666666666666</v>
       </c>
       <c r="C60" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10088.299999999999</v>
       </c>
       <c r="D60" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2582.5999999999995</v>
       </c>
       <c r="E60" s="21">
         <f>MAX($D$56:D60)</f>
         <v>2582.5999999999995</v>
       </c>
+      <c r="G60">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="5">
         <v>5</v>
       </c>
       <c r="B61" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>239.41666666666666</v>
       </c>
       <c r="C61" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>12713.1</v>
       </c>
       <c r="D61" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2624.8000000000011</v>
       </c>
       <c r="E61" s="21">
         <f>MAX($D$56:D61)</f>
         <v>2624.8000000000011</v>
       </c>
+      <c r="G61">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="5">
         <v>6</v>
       </c>
       <c r="B62" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>290.89999999999998</v>
       </c>
       <c r="C62" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15380.7</v>
       </c>
       <c r="D62" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2667.6000000000004</v>
       </c>
       <c r="E62" s="21">
         <f>MAX($D$56:D62)</f>
         <v>2667.6000000000004</v>
       </c>
+      <c r="G62">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="5">
         <v>7</v>
       </c>
       <c r="B63" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>343.61666666666667</v>
       </c>
       <c r="C63" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>18091.099999999999</v>
       </c>
       <c r="D63" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2710.3999999999978</v>
       </c>
       <c r="E63" s="21">
         <f>MAX($D$56:D63)</f>
         <v>2710.3999999999978</v>
       </c>
+      <c r="G63">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5">
         <v>8</v>
       </c>
       <c r="B64" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>397.61666666666667</v>
       </c>
       <c r="C64" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>20846.099999999999</v>
       </c>
       <c r="D64" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2755</v>
       </c>
       <c r="E64" s="21">
         <f>MAX($D$56:D64)</f>
         <v>2755</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G64">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5">
         <v>9</v>
       </c>
       <c r="B65" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>452.9</v>
       </c>
       <c r="C65" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>23645.7</v>
       </c>
       <c r="D65" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2799.6000000000022</v>
       </c>
       <c r="E65" s="21">
         <f>MAX($D$56:D65)</f>
         <v>2799.6000000000022</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G65">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5">
         <v>10</v>
       </c>
       <c r="B66" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>509.51666666666665</v>
       </c>
       <c r="C66" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>26491.599999999999</v>
       </c>
       <c r="D66" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2845.8999999999978</v>
       </c>
       <c r="E66" s="21">
         <f>MAX($D$56:D66)</f>
         <v>2845.8999999999978</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G66">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5">
         <v>11</v>
       </c>
       <c r="B67" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>567.48333333333335</v>
       </c>
       <c r="C67" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>29384.3</v>
       </c>
       <c r="D67" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2892.7000000000007</v>
       </c>
       <c r="E67" s="21">
         <f>MAX($D$56:D67)</f>
         <v>2892.7000000000007</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G67">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5">
         <v>12</v>
       </c>
       <c r="B68" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>626.79999999999995</v>
       </c>
       <c r="C68" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>32323.9</v>
       </c>
       <c r="D68" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2939.6000000000022</v>
       </c>
       <c r="E68" s="21">
         <f>MAX($D$56:D68)</f>
         <v>2939.6000000000022</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G68">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5">
         <v>13</v>
       </c>
       <c r="B69" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>687.5333333333333</v>
       </c>
       <c r="C69" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>35312.699999999997</v>
       </c>
       <c r="D69" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2988.7999999999956</v>
       </c>
       <c r="E69" s="21">
         <f>MAX($D$56:D69)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G69">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5">
         <v>14</v>
       </c>
       <c r="B70" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>749.66666666666663</v>
       </c>
       <c r="C70" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>37835</v>
       </c>
       <c r="D70" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2522.3000000000029</v>
       </c>
       <c r="E70" s="21">
         <f>MAX($D$56:D70)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G70">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5">
         <v>15</v>
       </c>
       <c r="B71" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>813.26666666666665</v>
       </c>
       <c r="C71" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>39819.199999999997</v>
       </c>
       <c r="D71" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1984.1999999999971</v>
       </c>
       <c r="E71" s="21">
         <f>MAX($D$56:D71)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G71">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5">
         <v>16</v>
       </c>
       <c r="B72" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>878.31666666666672</v>
       </c>
       <c r="C72" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>41828.6</v>
       </c>
       <c r="D72" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2009.4000000000015</v>
       </c>
       <c r="E72" s="21">
         <f>MAX($D$56:D72)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G72">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5">
         <v>17</v>
       </c>
       <c r="B73" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>944.88333333333333</v>
       </c>
       <c r="C73" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>43864.2</v>
       </c>
       <c r="D73" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2035.5999999999985</v>
       </c>
       <c r="E73" s="21">
         <f>MAX($D$56:D73)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G73">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5">
         <v>18</v>
       </c>
       <c r="B74" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1012.9666666666667</v>
       </c>
       <c r="C74" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>45926.2</v>
       </c>
       <c r="D74" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2062</v>
       </c>
       <c r="E74" s="21">
         <f>MAX($D$56:D74)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G74">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5">
         <v>19</v>
       </c>
       <c r="B75" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1082.6166666666666</v>
       </c>
       <c r="C75" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>48015.4</v>
       </c>
       <c r="D75" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2089.2000000000044</v>
       </c>
       <c r="E75" s="21">
         <f>MAX($D$56:D75)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G75">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5">
         <v>20</v>
       </c>
       <c r="B76" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1153.8333333333333</v>
       </c>
       <c r="C76" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50131.8</v>
       </c>
       <c r="D76" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2116.4000000000015</v>
       </c>
       <c r="E76" s="21">
         <f>MAX($D$56:D76)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G76">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5">
         <v>21</v>
       </c>
       <c r="B77" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1226.6666666666667</v>
       </c>
       <c r="C77" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>52276.3</v>
       </c>
       <c r="D77" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2144.5</v>
       </c>
       <c r="E77" s="21">
         <f>MAX($D$56:D77)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G77">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5">
         <v>22</v>
       </c>
       <c r="B78" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1301.1500000000001</v>
       </c>
       <c r="C78" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>54449.4</v>
       </c>
       <c r="D78" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2173.0999999999985</v>
       </c>
       <c r="E78" s="21">
         <f>MAX($D$56:D78)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G78">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5">
         <v>23</v>
       </c>
       <c r="B79" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1377.3</v>
       </c>
       <c r="C79" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>56651.5</v>
       </c>
       <c r="D79" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2202.0999999999985</v>
       </c>
       <c r="E79" s="21">
         <f>MAX($D$56:D79)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G79">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5">
         <v>24</v>
       </c>
       <c r="B80" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1455.1333333333334</v>
       </c>
       <c r="C80" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>58882.7</v>
       </c>
       <c r="D80" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2231.1999999999971</v>
       </c>
       <c r="E80" s="21">
         <f>MAX($D$56:D80)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G80">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5">
         <v>25</v>
       </c>
       <c r="B81" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1534.7166666666667</v>
       </c>
       <c r="C81" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>61144.4</v>
       </c>
       <c r="D81" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2261.7000000000044</v>
       </c>
       <c r="E81" s="21">
         <f>MAX($D$56:D81)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G81">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="5">
         <v>26</v>
       </c>
       <c r="B82" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1616.05</v>
       </c>
       <c r="C82" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>63436.4</v>
       </c>
       <c r="D82" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2292</v>
       </c>
       <c r="E82" s="21">
         <f>MAX($D$56:D82)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G82">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5">
         <v>27</v>
       </c>
       <c r="B83" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1699.1833333333334</v>
       </c>
       <c r="C83" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>65759.7</v>
       </c>
       <c r="D83" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2323.2999999999956</v>
       </c>
       <c r="E83" s="21">
         <f>MAX($D$56:D83)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G83">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5">
         <v>28</v>
       </c>
       <c r="B84" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1784.15</v>
       </c>
       <c r="C84" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>68114.8</v>
       </c>
       <c r="D84" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2355.1000000000058</v>
       </c>
       <c r="E84" s="21">
         <f>MAX($D$56:D84)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G84">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5">
         <v>29</v>
       </c>
       <c r="B85" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1870.9666666666667</v>
       </c>
       <c r="C85" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>70502.100000000006</v>
       </c>
       <c r="D85" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2387.3000000000029</v>
       </c>
       <c r="E85" s="21">
         <f>MAX($D$56:D85)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G85">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5">
         <v>30</v>
       </c>
       <c r="B86" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1959.6833333333334</v>
       </c>
       <c r="C86" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>72922.3</v>
       </c>
       <c r="D86" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2420.1999999999971</v>
       </c>
       <c r="E86" s="21">
         <f>MAX($D$56:D86)</f>
         <v>2988.7999999999956</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G86">
+        <f t="shared" si="10"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="27" t="s">
         <v>154</v>
       </c>
       <c r="D87" s="28">
         <f>SUMPRODUCT((E56:E86&lt;=MES_PRICE)*1)-1</f>
         <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
+        <v>149</v>
+      </c>
+      <c r="B91" t="s">
+        <v>191</v>
+      </c>
+      <c r="D91" t="s">
+        <v>152</v>
+      </c>
+      <c r="G91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92">
+        <f>Model!$B$32+Model!$D$32+ROUND(A92*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A92*60,0)/60</f>
+        <v>4294.05</v>
+      </c>
+      <c r="C92">
+        <f t="shared" ref="C92:C112" si="12">ROUND(FIXED_COST+(BEDS_TOM*TOM_FERT_COST)+(BEDS_MES*MES_FERT_COST)+A92*CAR_FERT_COST+ROUND(MIN(B92,FARMER_HRS_CAP)*FARMER_RATE,1)+ROUND(MAX(0,B92-FARMER_HRS_CAP)*TEMP_RATE,1),1)</f>
+        <v>142249.5</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <f t="shared" ref="G92:G112" si="13">CAR_PRICE</f>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93">
+        <f>Model!$B$32+Model!$D$32+ROUND(A93*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A93*60,0)/60</f>
+        <v>4324.8</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="12"/>
+        <v>143223.29999999999</v>
+      </c>
+      <c r="D93">
+        <f t="shared" ref="D93:D112" si="14">C93-C92</f>
+        <v>973.79999999998836</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94">
+        <v>2</v>
+      </c>
+      <c r="B94">
+        <f>Model!$B$32+Model!$D$32+ROUND(A94*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A94*60,0)/60</f>
+        <v>4357.0833333333339</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="12"/>
+        <v>144223.79999999999</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="14"/>
+        <v>1000.5</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95">
+        <v>3</v>
+      </c>
+      <c r="B95">
+        <f>Model!$B$32+Model!$D$32+ROUND(A95*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A95*60,0)/60</f>
+        <v>4390.9666666666672</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="12"/>
+        <v>145252.1</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="14"/>
+        <v>1028.3000000000175</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96">
+        <v>4</v>
+      </c>
+      <c r="B96">
+        <f>Model!$B$32+Model!$D$32+ROUND(A96*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A96*60,0)/60</f>
+        <v>4426.5</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="12"/>
+        <v>146309</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="14"/>
+        <v>1056.8999999999942</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97">
+        <f>Model!$B$32+Model!$D$32+ROUND(A97*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A97*60,0)/60</f>
+        <v>4463.7666666666664</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="12"/>
+        <v>147395.9</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="14"/>
+        <v>1086.8999999999942</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98">
+        <v>6</v>
+      </c>
+      <c r="B98">
+        <f>Model!$B$32+Model!$D$32+ROUND(A98*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A98*60,0)/60</f>
+        <v>4502.8</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="12"/>
+        <v>148513.60000000001</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="14"/>
+        <v>1117.7000000000116</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99">
+        <v>7</v>
+      </c>
+      <c r="B99">
+        <f>Model!$B$32+Model!$D$32+ROUND(A99*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A99*60,0)/60</f>
+        <v>4543.666666666667</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="12"/>
+        <v>149663.1</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="14"/>
+        <v>1149.5</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100">
+        <v>8</v>
+      </c>
+      <c r="B100">
+        <f>Model!$B$32+Model!$D$32+ROUND(A100*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A100*60,0)/60</f>
+        <v>4586.4666666666672</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="12"/>
+        <v>150846.20000000001</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="14"/>
+        <v>1183.1000000000058</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101">
+        <v>9</v>
+      </c>
+      <c r="B101">
+        <f>Model!$B$32+Model!$D$32+ROUND(A101*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A101*60,0)/60</f>
+        <v>4631.25</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="12"/>
+        <v>152063.6</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="14"/>
+        <v>1217.3999999999942</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102">
+        <v>10</v>
+      </c>
+      <c r="B102">
+        <f>Model!$B$32+Model!$D$32+ROUND(A102*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A102*60,0)/60</f>
+        <v>4678.0833333333339</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="12"/>
+        <v>153316.70000000001</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="14"/>
+        <v>1253.1000000000058</v>
+      </c>
+      <c r="G102">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103">
+        <v>11</v>
+      </c>
+      <c r="B103">
+        <f>Model!$B$32+Model!$D$32+ROUND(A103*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A103*60,0)/60</f>
+        <v>4727.0333333333338</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="12"/>
+        <v>154606.6</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="14"/>
+        <v>1289.8999999999942</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104">
+        <v>12</v>
+      </c>
+      <c r="B104">
+        <f>Model!$B$32+Model!$D$32+ROUND(A104*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A104*60,0)/60</f>
+        <v>4778.2166666666672</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="12"/>
+        <v>155935.20000000001</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="14"/>
+        <v>1328.6000000000058</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105">
+        <v>13</v>
+      </c>
+      <c r="B105">
+        <f>Model!$B$32+Model!$D$32+ROUND(A105*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A105*60,0)/60</f>
+        <v>4831.666666666667</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="12"/>
+        <v>157303.1</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="14"/>
+        <v>1367.8999999999942</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106">
+        <v>14</v>
+      </c>
+      <c r="B106">
+        <f>Model!$B$32+Model!$D$32+ROUND(A106*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A106*60,0)/60</f>
+        <v>4887.5</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="12"/>
+        <v>158712.4</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="14"/>
+        <v>1409.2999999999884</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107">
+        <v>15</v>
+      </c>
+      <c r="B107">
+        <f>Model!$B$32+Model!$D$32+ROUND(A107*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A107*60,0)/60</f>
+        <v>4945.7833333333338</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="12"/>
+        <v>160164.29999999999</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="14"/>
+        <v>1451.8999999999942</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108">
+        <v>16</v>
+      </c>
+      <c r="B108">
+        <f>Model!$B$32+Model!$D$32+ROUND(A108*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A108*60,0)/60</f>
+        <v>5006.6166666666668</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="12"/>
+        <v>161660.4</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="14"/>
+        <v>1496.1000000000058</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109">
+        <v>17</v>
+      </c>
+      <c r="B109">
+        <f>Model!$B$32+Model!$D$32+ROUND(A109*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A109*60,0)/60</f>
+        <v>5070.0833333333339</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="12"/>
+        <v>163202.29999999999</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="14"/>
+        <v>1541.8999999999942</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110">
+        <v>18</v>
+      </c>
+      <c r="B110">
+        <f>Model!$B$32+Model!$D$32+ROUND(A110*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A110*60,0)/60</f>
+        <v>5136.2666666666664</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="12"/>
+        <v>164791.29999999999</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="14"/>
+        <v>1589</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111">
+        <v>19</v>
+      </c>
+      <c r="B111">
+        <f>Model!$B$32+Model!$D$32+ROUND(A111*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A111*60,0)/60</f>
+        <v>5205.2833333333338</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="12"/>
+        <v>166429.5</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="14"/>
+        <v>1638.2000000000116</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="13"/>
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112">
+        <v>20</v>
+      </c>
+      <c r="B112">
+        <f>Model!$B$32+Model!$D$32+ROUND(A112*CAR_HRS*WEEKS*(1+CAR_DIM_PCT)^A112*60,0)/60</f>
+        <v>5277.2166666666672</v>
+      </c>
+      <c r="C112">
+        <f t="shared" si="12"/>
+        <v>168118.3</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="14"/>
+        <v>1688.7999999999884</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="13"/>
+        <v>2094</v>
       </c>
     </row>
   </sheetData>
@@ -4131,6 +6417,7 @@
     <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
